--- a/05_プロジェクト/carrot-club-analysis/2026-review/キャロット2026検討.xlsx
+++ b/05_プロジェクト/carrot-club-analysis/2026-review/キャロット2026検討.xlsx
@@ -774,7 +774,7 @@
         <v>420</v>
       </c>
       <c r="P2" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="25" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="W2" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
       <c r="X2" s="25" t="inlineStr">
@@ -865,7 +865,7 @@
         <v>468</v>
       </c>
       <c r="P3" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="25" t="inlineStr">
         <is>
@@ -889,12 +889,12 @@
       </c>
       <c r="W3" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
-        </is>
-      </c>
-      <c r="X3" s="24" t="inlineStr">
-        <is>
-          <t>※O列(馬体重)はカタログ発表後に入力すると基準スコアに自動加点。スコアは「検討基準」シート参照(6点満点)。</t>
+          <t>2500万+・420kg+</t>
+        </is>
+      </c>
+      <c r="X3" s="29" t="inlineStr">
+        <is>
+          <t>※スコアは4点満点（牡馬／総額2500万円以上／総額4000万円未満／馬体重420kg以上）。値は計算済みで入っている（式ではない）。定義と根拠は「検討基準」シート。</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
         <v>424</v>
       </c>
       <c r="P4" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="25" t="inlineStr">
         <is>
@@ -984,12 +984,12 @@
       </c>
       <c r="W4" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
-        </is>
-      </c>
-      <c r="X4" s="25" t="inlineStr">
-        <is>
-          <t>※厩舎相性=2020-22年実績より(◎=回収・勝ち上がりとも優秀/○=堅実/△=注意)。詳細は「検討基準」シート。地方馬の厩舎は移籍前提のため評価対象外。</t>
+          <t>2500万+・420kg+</t>
+        </is>
+      </c>
+      <c r="X4" s="29" t="inlineStr">
+        <is>
+          <t>※厩舎相性=2020〜2024年度の5年・中央400口・5頭以上預託の厩舎のみ（◎=回収≥1が30%以上／○=回収≥1が20%以上または中央勝ち上がり65%以上／△=注意）。詳細は「検討基準」シート。地方馬の厩舎は移籍前提のため評価対象外。</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
         <v>430</v>
       </c>
       <c r="P5" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="25" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="W5" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
         <v>430</v>
       </c>
       <c r="P6" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="25" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="W6" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         <v>440</v>
       </c>
       <c r="P7" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="25" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="W7" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>454</v>
       </c>
       <c r="P8" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="25" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="W8" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
         <v>473</v>
       </c>
       <c r="P9" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="25" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="W9" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
         <v>415</v>
       </c>
       <c r="P10" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="25" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="W10" s="29" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
         <v>444</v>
       </c>
       <c r="P11" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="25" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="W11" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
         <v>402</v>
       </c>
       <c r="P12" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="25" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="W12" s="29" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>452</v>
       </c>
       <c r="P13" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="25" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="W13" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         <v>443</v>
       </c>
       <c r="P14" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="25" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="W14" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>479</v>
       </c>
       <c r="P15" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="25" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="W15" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
         <v>415</v>
       </c>
       <c r="P16" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="25" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W16" s="29" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
         <v>467</v>
       </c>
       <c r="P17" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="25" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="W17" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
         <v>438</v>
       </c>
       <c r="P18" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="25" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="W18" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         <v>471</v>
       </c>
       <c r="P19" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="25" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="W19" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>436</v>
       </c>
       <c r="P20" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="25" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="W20" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
         <v>423</v>
       </c>
       <c r="P21" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="W21" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
         <v>431</v>
       </c>
       <c r="P22" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="25" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="W22" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
         <v>410</v>
       </c>
       <c r="P23" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="25" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="W23" s="29" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
         <v>442</v>
       </c>
       <c r="P24" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="25" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="W24" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
         <v>442</v>
       </c>
       <c r="P25" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="25" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W25" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
         <v>447</v>
       </c>
       <c r="P26" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="25" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="W26" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
         <v>426</v>
       </c>
       <c r="P27" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="25" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W27" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
         <v>474</v>
       </c>
       <c r="P28" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q28" s="25" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="W28" s="29" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
         <v>432</v>
       </c>
       <c r="P29" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="25" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="W29" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
         <v>421</v>
       </c>
       <c r="P30" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" s="25" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W30" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
         <v>429</v>
       </c>
       <c r="P31" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="W31" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
         <v>422</v>
       </c>
       <c r="P32" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="W32" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
         <v>407</v>
       </c>
       <c r="P33" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="25" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="W33" s="29" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>487</v>
       </c>
       <c r="P34" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="25" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="W34" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
         <v>425</v>
       </c>
       <c r="P36" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="25" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W36" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
         <v>489</v>
       </c>
       <c r="P37" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="25" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="W37" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
         <v>456</v>
       </c>
       <c r="P41" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q41" s="25" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="W41" s="29" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         <v>440</v>
       </c>
       <c r="P42" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="25" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="W42" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
         <v>438</v>
       </c>
       <c r="P43" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="25" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="W43" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
         <v>412</v>
       </c>
       <c r="P44" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="25" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W44" s="29" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
         <v>445</v>
       </c>
       <c r="P45" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="25" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="W45" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
         <v>410</v>
       </c>
       <c r="P46" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="25" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="W46" s="29" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
         <v>393</v>
       </c>
       <c r="P47" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="25" t="inlineStr">
         <is>
@@ -4839,7 +4839,11 @@
       <c r="V47" s="24" t="n">
         <v>19.2</v>
       </c>
-      <c r="W47" s="29" t="inlineStr"/>
+      <c r="W47" s="29" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="19">
       <c r="A48" s="24" t="n">
@@ -4903,7 +4907,7 @@
         <v>452</v>
       </c>
       <c r="P48" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="25" t="inlineStr">
         <is>
@@ -4931,7 +4935,7 @@
       </c>
       <c r="W48" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5091,7 @@
         <v>445</v>
       </c>
       <c r="P50" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q50" s="25" t="inlineStr">
         <is>
@@ -5115,7 +5119,7 @@
       </c>
       <c r="W50" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5185,7 @@
         <v>442</v>
       </c>
       <c r="P51" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" s="25" t="inlineStr">
         <is>
@@ -5205,7 +5209,7 @@
       </c>
       <c r="W51" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5275,7 @@
         <v>480</v>
       </c>
       <c r="P52" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="25" t="inlineStr">
         <is>
@@ -5295,7 +5299,7 @@
       </c>
       <c r="W52" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5361,7 @@
         <v>466</v>
       </c>
       <c r="P53" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="25" t="inlineStr">
         <is>
@@ -5385,7 +5389,7 @@
       </c>
       <c r="W53" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5451,7 @@
         <v>480</v>
       </c>
       <c r="P54" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q54" s="25" t="inlineStr">
         <is>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="W54" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5541,7 @@
         <v>463</v>
       </c>
       <c r="P55" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="25" t="inlineStr">
         <is>
@@ -5561,7 +5565,7 @@
       </c>
       <c r="W55" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5627,7 @@
         <v>452</v>
       </c>
       <c r="P56" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q56" s="25" t="inlineStr">
         <is>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="W56" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5717,7 @@
         <v>430</v>
       </c>
       <c r="P57" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="25" t="inlineStr">
         <is>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="W57" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5811,7 @@
         <v>414</v>
       </c>
       <c r="P58" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="25" t="inlineStr">
         <is>
@@ -5831,7 +5835,7 @@
       </c>
       <c r="W58" s="29" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5901,7 @@
         <v>414</v>
       </c>
       <c r="P59" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="25" t="inlineStr">
         <is>
@@ -5919,7 +5923,11 @@
       <c r="V59" s="24" t="n">
         <v>20.4</v>
       </c>
-      <c r="W59" s="29" t="inlineStr"/>
+      <c r="W59" s="29" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="19">
       <c r="A60" s="24" t="n">
@@ -5979,7 +5987,7 @@
         <v>426</v>
       </c>
       <c r="P60" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q60" s="25" t="inlineStr">
         <is>
@@ -6003,7 +6011,7 @@
       </c>
       <c r="W60" s="29" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6073,7 @@
         <v>421</v>
       </c>
       <c r="P61" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="25" t="inlineStr">
         <is>
@@ -6093,7 +6101,7 @@
       </c>
       <c r="W61" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6163,7 @@
         <v>446</v>
       </c>
       <c r="P62" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="25" t="inlineStr">
         <is>
@@ -6183,7 +6191,7 @@
       </c>
       <c r="W62" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6253,7 @@
         <v>457</v>
       </c>
       <c r="P63" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q63" s="25" t="inlineStr">
         <is>
@@ -6273,7 +6281,7 @@
       </c>
       <c r="W63" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6343,7 @@
         <v>410</v>
       </c>
       <c r="P64" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="25" t="inlineStr">
         <is>
@@ -6363,7 +6371,7 @@
       </c>
       <c r="W64" s="29" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6437,7 @@
         <v>413</v>
       </c>
       <c r="P65" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="25" t="inlineStr">
         <is>
@@ -6451,7 +6459,11 @@
       <c r="V65" s="24" t="n">
         <v>19.8</v>
       </c>
-      <c r="W65" s="29" t="inlineStr"/>
+      <c r="W65" s="29" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="19">
       <c r="A66" s="24" t="n">
@@ -6515,7 +6527,7 @@
         <v>506</v>
       </c>
       <c r="P66" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q66" s="25" t="inlineStr">
         <is>
@@ -6539,7 +6551,7 @@
       </c>
       <c r="W66" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6613,7 @@
         <v>447</v>
       </c>
       <c r="P67" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q67" s="25" t="inlineStr">
         <is>
@@ -6625,7 +6637,7 @@
       </c>
       <c r="W67" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6703,7 @@
         <v>447</v>
       </c>
       <c r="P68" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q68" s="25" t="inlineStr">
         <is>
@@ -6715,7 +6727,7 @@
       </c>
       <c r="W68" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6793,7 @@
         <v>447</v>
       </c>
       <c r="P69" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q69" s="25" t="inlineStr">
         <is>
@@ -6805,7 +6817,7 @@
       </c>
       <c r="W69" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6883,7 @@
         <v>447</v>
       </c>
       <c r="P70" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" s="25" t="inlineStr">
         <is>
@@ -6895,7 +6907,7 @@
       </c>
       <c r="W70" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6973,7 @@
         <v>492</v>
       </c>
       <c r="P71" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="25" t="inlineStr">
         <is>
@@ -6989,7 +7001,7 @@
       </c>
       <c r="W71" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7067,7 @@
         <v>458</v>
       </c>
       <c r="P72" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q72" s="25" t="inlineStr">
         <is>
@@ -7079,7 +7091,7 @@
       </c>
       <c r="W72" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7157,7 @@
         <v>454</v>
       </c>
       <c r="P73" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="25" t="inlineStr">
         <is>
@@ -7169,7 +7181,7 @@
       </c>
       <c r="W73" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7247,7 @@
         <v>448</v>
       </c>
       <c r="P74" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="25" t="inlineStr">
         <is>
@@ -7263,7 +7275,7 @@
       </c>
       <c r="W74" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7341,7 @@
         <v>440</v>
       </c>
       <c r="P75" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="25" t="inlineStr">
         <is>
@@ -7353,7 +7365,7 @@
       </c>
       <c r="W75" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7431,7 @@
         <v>455</v>
       </c>
       <c r="P76" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q76" s="25" t="inlineStr">
         <is>
@@ -7447,7 +7459,7 @@
       </c>
       <c r="W76" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7525,7 @@
         <v>458</v>
       </c>
       <c r="P77" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="25" t="inlineStr">
         <is>
@@ -7537,7 +7549,7 @@
       </c>
       <c r="W77" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7611,7 @@
         <v>430</v>
       </c>
       <c r="P78" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q78" s="25" t="inlineStr">
         <is>
@@ -7623,7 +7635,7 @@
       </c>
       <c r="W78" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7697,7 @@
         <v>449</v>
       </c>
       <c r="P79" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q79" s="25" t="inlineStr">
         <is>
@@ -7709,7 +7721,7 @@
       </c>
       <c r="W79" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7783,7 @@
         <v>432</v>
       </c>
       <c r="P80" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q80" s="25" t="inlineStr">
         <is>
@@ -7795,7 +7807,7 @@
       </c>
       <c r="W80" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7873,7 @@
         <v>403</v>
       </c>
       <c r="P81" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="25" t="inlineStr">
         <is>
@@ -7883,7 +7895,11 @@
       <c r="V81" s="24" t="n">
         <v>19.6</v>
       </c>
-      <c r="W81" s="29" t="inlineStr"/>
+      <c r="W81" s="29" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="19">
       <c r="A82" s="24" t="n">
@@ -7947,7 +7963,7 @@
         <v>470</v>
       </c>
       <c r="P82" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" s="25" t="inlineStr">
         <is>
@@ -7971,7 +7987,7 @@
       </c>
       <c r="W82" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8139,7 @@
         <v>470</v>
       </c>
       <c r="P84" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q84" s="25" t="inlineStr">
         <is>
@@ -8151,7 +8167,7 @@
       </c>
       <c r="W84" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8233,7 @@
         <v>429</v>
       </c>
       <c r="P85" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q85" s="25" t="inlineStr">
         <is>
@@ -8245,7 +8261,7 @@
       </c>
       <c r="W85" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8327,7 @@
         <v>442</v>
       </c>
       <c r="P86" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q86" s="25" t="inlineStr">
         <is>
@@ -8335,7 +8351,7 @@
       </c>
       <c r="W86" s="29" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8417,7 @@
         <v>436</v>
       </c>
       <c r="P87" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" s="25" t="inlineStr">
         <is>
@@ -8425,7 +8441,7 @@
       </c>
       <c r="W87" s="29" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8777,7 @@
         <v>490</v>
       </c>
       <c r="P91" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q91" s="25" t="inlineStr">
         <is>
@@ -8785,7 +8801,7 @@
       </c>
       <c r="W91" s="29" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8863,7 @@
         <v>437</v>
       </c>
       <c r="P92" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q92" s="25" t="inlineStr">
         <is>
@@ -8871,7 +8887,7 @@
       </c>
       <c r="W92" s="29" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="18" min="1" max="1"/>
@@ -9209,7 +9225,7 @@
     <row r="8" ht="14.25" customHeight="1" s="19">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>◆スコア基準(各1点・計3点)</t>
+          <t>◆スコア基準(各1点・計4点)</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
@@ -9243,340 +9259,320 @@
     <row r="10" ht="14.25" customHeight="1" s="19">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>2. 募集総額</t>
+          <t>2. 募集総額の下限</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>2500〜3999万円</t>
+          <t>2500万円以上</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>57%・24%（148頭）。2500万未満は31%・15%（113頭）と落ち、4000万以上は54%・13%（183頭）で走るが回収が伸びない</t>
+          <t>2500万未満は31%・15%（113頭）で、走らない。5年とも例外なく最下位（2020年31%/2021年33%/2022年33%/2023年42%/2024年14%）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="19">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>3. 馬体重</t>
+          <t>3. 募集総額の上限</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
+          <t>4000万円未満</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>2500〜3999万は57%・24%（148頭）。4000万以上は54%・13%（183頭）で、走る確率は変わらないのに回収だけ落ちる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" s="19">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>4. 馬体重</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
           <t>募集時420kg以上</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>54%・19%（352頭）vs 420kg未満31%・10%（91頭）</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1" s="19">
-      <c r="A12" s="31" t="inlineStr"/>
-      <c r="B12" s="31" t="inlineStr"/>
-      <c r="C12" s="31" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>◆5年に広げて落とした基準（3年では効いて見えたが5年では効かなかった）</t>
-        </is>
-      </c>
+      <c r="A13" s="31" t="inlineStr"/>
       <c r="B13" s="31" t="inlineStr"/>
       <c r="C13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="19">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>3〜4月生まれ</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>3〜4月生51%（216頭）vs 1〜2月生48%（196頭）</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>年度ダミーつきロジスティック回帰で z=+0.7（有意でない）</t>
-        </is>
-      </c>
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>◆5年に広げて落とした基準（3年では効いて見えたが5年では効かなかった）</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="19">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>ノーザンＦ生産</t>
+          <t>3〜4月生まれ</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>ノーザンＦ49%（391頭）vs その他51%（53頭）</t>
+          <t>3〜4月生51%（216頭）vs 1〜2月生48%（196頭）</t>
         </is>
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>z=−0.1。白老Ｆ・追分Ｆのほうがむしろ上</t>
+          <t>年度ダミーつきロジスティック回帰で z=+0.7（有意でない）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="19">
       <c r="A16" s="31" t="inlineStr">
         <is>
+          <t>ノーザンＦ生産</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>ノーザンＦ49%（391頭）vs その他51%（53頭）</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>z=−0.1。白老Ｆ・追分Ｆのほうがむしろ上</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" s="19">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
           <t>母8〜11歳</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>52%（180頭）vs それ以外47%</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>z=+0.9（有意でない）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1" s="19">
-      <c r="A17" s="31" t="inlineStr"/>
-      <c r="B17" s="31" t="inlineStr"/>
-      <c r="C17" s="31" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>◆スコア別の実績（5年・中央400口）</t>
-        </is>
-      </c>
+      <c r="A18" s="31" t="inlineStr"/>
       <c r="B18" s="31" t="inlineStr"/>
       <c r="C18" s="31" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>スコア3 (52頭)</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>中央勝ち上がり67%・回収≥1が37%・回収中央値0.7</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>重賞6頭</t>
-        </is>
-      </c>
+          <t>※価格を下限と上限の2本に割った理由：効き方が違う。下限は「走るか」に効き（入れ子leave-one-year-outで中央勝ち上がりのAUCが5年すべて改善、平均+0.019）、上限は「回収するか」にだけ効く（回収率は分母が価格なので機械的な分も含む）</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr"/>
+      <c r="C19" s="31" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="19">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>スコア2 (202頭)</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>中央勝ち上がり54%・回収≥1が16%・回収中央値0.24</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>重賞12頭</t>
-        </is>
-      </c>
+      <c r="A20" s="31" t="inlineStr"/>
+      <c r="B20" s="31" t="inlineStr"/>
+      <c r="C20" s="31" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="19">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>スコア1 (147頭)</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>中央勝ち上がり45%・回収≥1が16%・回収中央値0.22</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>重賞2頭</t>
-        </is>
-      </c>
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>◆スコア別の実績（5年・中央400口）</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr"/>
+      <c r="C21" s="31" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="19">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>スコア0 (43頭)</t>
+          <t>スコア4 (52頭)</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>中央勝ち上がり21%・回収≥1が2%・回収中央値0.04</t>
+          <t>中央勝ち上がり67%・回収≥1が37%・回収中央値0.7</t>
         </is>
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞6頭</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="19">
-      <c r="A23" s="31" t="inlineStr"/>
-      <c r="B23" s="31" t="inlineStr"/>
-      <c r="C23" s="31" t="inlineStr"/>
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>スコア3 (179頭)</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>中央勝ち上がり57%・回収≥1が16%・回収中央値0.26</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>重賞12頭</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="19">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>◆当たり具合（AUC。0.5＝でたらめ、1.0＝完全）</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr"/>
-      <c r="C24" s="31" t="inlineStr"/>
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>スコア2 (107頭)</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>中央勝ち上がり46%・回収≥1が14%・回収中央値0.19</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>重賞1頭</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="19">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>新スコア(3点)</t>
+          <t>スコア1 (79頭)</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>中央勝ち上がり0.614 / 回収≥1 0.621</t>
+          <t>中央勝ち上がり37%・回収≥1が15%・回収中央値0.17</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>年度別 2020:0.57 2021:0.57 2022:0.7 2023:0.54 2024:0.67</t>
+          <t>重賞1頭</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="19">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>既存6基準</t>
+          <t>スコア0 (27頭)</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>中央勝ち上がり0.608 / 回収≥1 0.598</t>
+          <t>中央勝ち上がり15%・回収≥1が4%・回収中央値0.03</t>
         </is>
       </c>
       <c r="C26" s="31" t="inlineStr">
         <is>
-          <t>年度別 2020:0.73 2021:0.56 2022:0.66 2023:0.56 2024:0.53</t>
+          <t>重賞0頭</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>※既存6基準は作った年（2020年度）で高く、作成に使っていない2023・2024年度で落ちる。基準を絞ったほうが年をまたいで安定する</t>
-        </is>
-      </c>
+      <c r="A27" s="31" t="inlineStr"/>
       <c r="B27" s="31" t="inlineStr"/>
       <c r="C27" s="31" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="19">
-      <c r="A28" s="31" t="inlineStr"/>
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>◆当たり具合（AUC。0.5＝でたらめ、1.0＝完全）</t>
+        </is>
+      </c>
       <c r="B28" s="31" t="inlineStr"/>
       <c r="C28" s="31" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="19">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>◆募集価格の帯ごとの中身</t>
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>新スコア(4点満点)</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>中央勝ち上がり / 回収≥1 / 回収中央値</t>
+          <t>中央勝ち上がり0.635 / 回収≥1 0.609</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>重賞</t>
+          <t>年度別 2020:0.62 2021:0.59 2022:0.71 2023:0.56 2024:0.69</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="19">
       <c r="A30" s="31" t="inlineStr">
         <is>
-          <t>2500万未満 (113頭)</t>
+          <t>旧6基準（2020〜2022年度で作ったもの）</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>31% / 15% / 0.15</t>
+          <t>中央勝ち上がり0.608 / 回収≥1 0.598</t>
         </is>
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>1頭</t>
+          <t>年度別 2020:0.73 2021:0.56 2022:0.66 2023:0.56 2024:0.53</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="19">
       <c r="A31" s="31" t="inlineStr">
         <is>
-          <t>2500〜3999万 (148頭)</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="inlineStr">
-        <is>
-          <t>57% / 24% / 0.36</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>9頭</t>
-        </is>
-      </c>
+          <t>※既存6基準は作った年（2020年度）で高く、作成に使っていない2023・2024年度で落ちる。基準を絞ったほうが年をまたいで安定する</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr"/>
+      <c r="C31" s="31" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="19">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>4000〜4999万 (66頭)</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>53% / 12% / 0.17</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>1頭</t>
-        </is>
-      </c>
+      <c r="A32" s="31" t="inlineStr"/>
+      <c r="B32" s="31" t="inlineStr"/>
+      <c r="C32" s="31" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="19">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>5000〜5999万 (60頭)</t>
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>◆募集価格の帯ごとの中身</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>53% / 17% / 0.18</t>
+          <t>中央勝ち上がり / 回収≥1 / 回収中央値</t>
         </is>
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>5頭</t>
+          <t>重賞</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="19">
       <c r="A34" s="31" t="inlineStr">
         <is>
-          <t>6000〜7999万 (35頭)</t>
+          <t>2500万未満 (113頭)</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>57% / 9% / 0.14</t>
+          <t>31% / 15% / 0.15</t>
         </is>
       </c>
       <c r="C34" s="31" t="inlineStr">
@@ -9588,92 +9584,128 @@
     <row r="35" ht="15" customHeight="1" s="19">
       <c r="A35" s="31" t="inlineStr">
         <is>
-          <t>8000万以上 (22頭)</t>
+          <t>2500〜3999万 (148頭)</t>
         </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>55% / 14% / 0.19</t>
+          <t>57% / 24% / 0.36</t>
         </is>
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>3頭</t>
+          <t>9頭</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>→ 5000万以上は「走るが回収が伸びない」。8000万以上で回収が募集額を超えたのは22頭中3頭</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="inlineStr"/>
-      <c r="C36" s="31" t="inlineStr"/>
+          <t>4000〜4999万 (66頭)</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>53% / 12% / 0.17</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>1頭</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="19">
-      <c r="A37" s="31" t="inlineStr"/>
-      <c r="B37" s="31" t="inlineStr"/>
-      <c r="C37" s="31" t="inlineStr"/>
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>5000〜5999万 (60頭)</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>53% / 17% / 0.18</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>5頭</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="19">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>◆価格帯の注意：募集価格の水準が上がり続けている</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr"/>
-      <c r="C38" s="31" t="inlineStr"/>
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>6000〜7999万 (35頭)</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>57% / 9% / 0.14</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>1頭</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="19">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>募集総額の中央値</t>
+          <t>8000万以上 (22頭)</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>2020年度2800万 → 2021年度3000万 → 2022年度3200万 → 2023年度3600万 → 2024年度4000万 → 2026年度5000万</t>
-        </is>
-      </c>
-      <c r="C39" s="31" t="inlineStr"/>
+          <t>55% / 14% / 0.19</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>3頭</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="19">
       <c r="A40" s="31" t="inlineStr">
         <is>
-          <t>価格基準を「その年の中での位置」に置き換えても当たり具合は改善しなかった（AUC 0.591 vs 絶対額0.614）ので絶対額のままにしている</t>
+          <t>→ 5000万以上は「走るが回収が伸びない」。8000万以上で回収が募集額を超えたのは22頭中3頭</t>
         </is>
       </c>
       <c r="B40" s="31" t="inlineStr"/>
       <c r="C40" s="31" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
-        <is>
-          <t>価格ちょうどの水準で見ると、3000万(52頭)が中央勝ち上がり69%・回収≥1が31%で突出し、4000万(50頭)は50%・12%で5000万(55頭)51%・15%とほぼ同じ。4000万は「3000万の延長」ではなく「5000万と同じ側」</t>
-        </is>
-      </c>
+      <c r="A41" s="31" t="inlineStr"/>
       <c r="B41" s="31" t="inlineStr"/>
       <c r="C41" s="31" t="inlineStr"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="19">
-      <c r="A42" s="31" t="inlineStr">
-        <is>
-          <t>ただし2026年度で2500〜3999万に該当するのは94頭中20頭。募集価格の上昇が続くと該当が減るので、来年以降は帯の見直しが要る</t>
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>◆価格帯の注意：募集価格の水準が上がり続けている</t>
         </is>
       </c>
       <c r="B42" s="31" t="inlineStr"/>
       <c r="C42" s="31" t="inlineStr"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="19">
-      <c r="A43" s="31" t="inlineStr"/>
-      <c r="B43" s="31" t="inlineStr"/>
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>募集総額の中央値</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>2020年度2800万 → 2021年度3000万 → 2022年度3200万 → 2023年度3600万 → 2024年度4000万 → 2026年度5000万</t>
+        </is>
+      </c>
       <c r="C43" s="31" t="inlineStr"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="19">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>◆回避条件</t>
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>価格基準を「その年の中での位置」に置き換えても当たり具合は改善しなかった（AUC 0.591 vs 絶対額0.614）ので絶対額のままにしている</t>
         </is>
       </c>
       <c r="B44" s="31" t="inlineStr"/>
@@ -9682,162 +9714,118 @@
     <row r="45" ht="15" customHeight="1" s="19">
       <c r="A45" s="31" t="inlineStr">
         <is>
-          <t>メスの馬体重420kg未満 (64頭)</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>中央勝ち上がり30%・回収≥1が6%・回収中央値0.08</t>
-        </is>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>420kg以上のメス（173頭）は50%・16%</t>
-        </is>
-      </c>
+          <t>※入れ子leave-one-year-out（その年を見ずに閾値も選ぶ）での中央勝ち上がりAUCは価格を1本にした3点版 0.611 → 下限を割った4点版 0.631。5年すべてで改善した。回収≥1のほうは 0.655 → 0.646 でわずかに悪化する</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr"/>
+      <c r="C45" s="31" t="inlineStr"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="19">
-      <c r="A46" s="31" t="inlineStr"/>
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>価格ちょうどの水準で見ると、3000万(52頭)が中央勝ち上がり69%・回収≥1が31%で突出し、4000万(50頭)は50%・12%で5000万(55頭)51%・15%とほぼ同じ。4000万は「3000万の延長」ではなく「5000万と同じ側」</t>
+        </is>
+      </c>
       <c r="B46" s="31" t="inlineStr"/>
       <c r="C46" s="31" t="inlineStr"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="19">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t>◆厩舎との相性（5年・中央400口・5頭以上。予定厩舎ベース）</t>
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>ただし2026年度で2500〜3999万に該当するのは94頭中20頭。募集価格の上昇が続くと該当が減るので、来年以降は帯の見直しが要る</t>
         </is>
       </c>
       <c r="B47" s="31" t="inlineStr"/>
       <c r="C47" s="31" t="inlineStr"/>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="19">
-      <c r="A48" s="31" t="inlineStr">
-        <is>
-          <t>【好調】池添学</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="inlineStr">
-        <is>
-          <t>14頭: 中央勝ち上がり64%・回収≥1が43%・回収中央値0.44</t>
-        </is>
-      </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>重賞2頭</t>
-        </is>
-      </c>
+      <c r="A48" s="31" t="inlineStr"/>
+      <c r="B48" s="31" t="inlineStr"/>
+      <c r="C48" s="31" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="19">
-      <c r="A49" s="31" t="inlineStr">
-        <is>
-          <t>【好調】田村康仁</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>5頭: 中央勝ち上がり60%・回収≥1が40%・回収中央値0.16</t>
-        </is>
-      </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>重賞0頭</t>
-        </is>
-      </c>
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>◆回避条件</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr"/>
+      <c r="C49" s="31" t="inlineStr"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="19">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t>【好調】安田翔伍</t>
+          <t>メスの馬体重420kg未満 (64頭)</t>
         </is>
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>6頭: 中央勝ち上がり83%・回収≥1が33%・回収中央値0.62</t>
+          <t>中央勝ち上がり30%・回収≥1が6%・回収中央値0.08</t>
         </is>
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>420kg以上のメス（173頭）は50%・16%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="19">
-      <c r="A51" s="31" t="inlineStr">
-        <is>
-          <t>【好調】武幸四郎</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>6頭: 中央勝ち上がり83%・回収≥1が33%・回収中央値0.7</t>
-        </is>
-      </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>重賞0頭</t>
-        </is>
-      </c>
+      <c r="A51" s="31" t="inlineStr"/>
+      <c r="B51" s="31" t="inlineStr"/>
+      <c r="C51" s="31" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="19">
-      <c r="A52" s="31" t="inlineStr">
-        <is>
-          <t>【好調】尾関知人</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>6頭: 中央勝ち上がり50%・回収≥1が33%・回収中央値0.17</t>
-        </is>
-      </c>
-      <c r="C52" s="31" t="inlineStr">
-        <is>
-          <t>重賞1頭</t>
-        </is>
-      </c>
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>◆厩舎との相性（5年・中央400口・5頭以上。予定厩舎ベース）</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr"/>
+      <c r="C52" s="31" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="19">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t>【好調】矢作芳人</t>
+          <t>【好調】池添学</t>
         </is>
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>6頭: 中央勝ち上がり33%・回収≥1が33%・回収中央値0.05</t>
+          <t>14頭: 中央勝ち上がり64%・回収≥1が43%・回収中央値0.44</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>重賞1頭</t>
+          <t>重賞2頭</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>【好調】国枝栄</t>
+          <t>【好調】田村康仁</t>
         </is>
       </c>
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>7頭: 中央勝ち上がり57%・回収≥1が29%・回収中央値0.26</t>
+          <t>5頭: 中央勝ち上がり60%・回収≥1が40%・回収中央値0.16</t>
         </is>
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>重賞2頭</t>
+          <t>重賞0頭</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t>【好調】藤原英昭</t>
+          <t>【好調】安田翔伍</t>
         </is>
       </c>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>7頭: 中央勝ち上がり57%・回収≥1が29%・回収中央値0.29</t>
+          <t>6頭: 中央勝ち上がり83%・回収≥1が33%・回収中央値0.62</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
@@ -9849,12 +9837,12 @@
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
-          <t>【注意】池江泰寿</t>
+          <t>【好調】武幸四郎</t>
         </is>
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>6頭: 中央勝ち上がり0%・回収≥1が0%・回収中央値0.06</t>
+          <t>6頭: 中央勝ち上がり83%・回収≥1が33%・回収中央値0.7</t>
         </is>
       </c>
       <c r="C56" s="31" t="inlineStr">
@@ -9866,63 +9854,63 @@
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
         <is>
-          <t>【注意】平田修</t>
+          <t>【好調】尾関知人</t>
         </is>
       </c>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>5頭: 中央勝ち上がり0%・回収≥1が0%・回収中央値0.0</t>
+          <t>6頭: 中央勝ち上がり50%・回収≥1が33%・回収中央値0.17</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞1頭</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t>【注意】萩原清</t>
+          <t>【好調】矢作芳人</t>
         </is>
       </c>
       <c r="B58" s="31" t="inlineStr">
         <is>
-          <t>9頭: 中央勝ち上がり11%・回収≥1が0%・回収中央値0.0</t>
+          <t>6頭: 中央勝ち上がり33%・回収≥1が33%・回収中央値0.05</t>
         </is>
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞1頭</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t>【注意】渡辺薫彦</t>
+          <t>【好調】国枝栄</t>
         </is>
       </c>
       <c r="B59" s="31" t="inlineStr">
         <is>
-          <t>5頭: 中央勝ち上がり20%・回収≥1が0%・回収中央値0.27</t>
+          <t>7頭: 中央勝ち上がり57%・回収≥1が29%・回収中央値0.26</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞2頭</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t>【注意】高柳瑞樹</t>
+          <t>【好調】藤原英昭</t>
         </is>
       </c>
       <c r="B60" s="31" t="inlineStr">
         <is>
-          <t>5頭: 中央勝ち上がり40%・回収≥1が0%・回収中央値0.12</t>
+          <t>7頭: 中央勝ち上がり57%・回収≥1が29%・回収中央値0.29</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
@@ -9934,12 +9922,12 @@
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>【注意】林徹</t>
+          <t>【注意】池江泰寿</t>
         </is>
       </c>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>5頭: 中央勝ち上がり40%・回収≥1が0%・回収中央値0.32</t>
+          <t>6頭: 中央勝ち上がり0%・回収≥1が0%・回収中央値0.06</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
@@ -9951,35 +9939,63 @@
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>※各厩舎5〜17頭の小標本。予定厩舎は募集時点のもので、実際の入厩先は変わりうる</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="inlineStr"/>
-      <c r="C62" s="31" t="inlineStr"/>
+          <t>【注意】平田修</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>5頭: 中央勝ち上がり0%・回収≥1が0%・回収中央値0.0</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="31" t="inlineStr"/>
-      <c r="B63" s="31" t="inlineStr"/>
-      <c r="C63" s="31" t="inlineStr"/>
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>【注意】萩原清</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>9頭: 中央勝ち上がり11%・回収≥1が0%・回収中央値0.0</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>◆父の傾向（5年・中央400口・8頭以上）</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="inlineStr"/>
-      <c r="C64" s="31" t="inlineStr"/>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>【注意】渡辺薫彦</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>5頭: 中央勝ち上がり20%・回収≥1が0%・回収中央値0.27</t>
+        </is>
+      </c>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>ニューイヤーズデイ</t>
+          <t>【注意】高柳瑞樹</t>
         </is>
       </c>
       <c r="B65" s="31" t="inlineStr">
         <is>
-          <t>10頭: 中央勝ち上がり90%・回収≥1が40%・回収中央値0.63</t>
+          <t>5頭: 中央勝ち上がり40%・回収≥1が0%・回収中央値0.12</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
@@ -9991,114 +10007,86 @@
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>リアルスティール</t>
+          <t>【注意】林徹</t>
         </is>
       </c>
       <c r="B66" s="31" t="inlineStr">
         <is>
-          <t>12頭: 中央勝ち上がり67%・回収≥1が33%・回収中央値0.39</t>
+          <t>5頭: 中央勝ち上がり40%・回収≥1が0%・回収中央値0.32</t>
         </is>
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>重賞2頭</t>
+          <t>重賞0頭</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>ルーラーシップ</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>15頭: 中央勝ち上がり47%・回収≥1が27%・回収中央値0.16</t>
-        </is>
-      </c>
-      <c r="C67" s="31" t="inlineStr">
-        <is>
-          <t>重賞1頭</t>
-        </is>
-      </c>
+          <t>※各厩舎5〜17頭の小標本。予定厩舎は募集時点のもので、実際の入厩先は変わりうる</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="inlineStr"/>
+      <c r="C67" s="31" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>ハービンジャー</t>
-        </is>
-      </c>
-      <c r="B68" s="31" t="inlineStr">
-        <is>
-          <t>16頭: 中央勝ち上がり44%・回収≥1が25%・回収中央値0.32</t>
-        </is>
-      </c>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>重賞2頭</t>
-        </is>
-      </c>
+      <c r="A68" s="31" t="inlineStr"/>
+      <c r="B68" s="31" t="inlineStr"/>
+      <c r="C68" s="31" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>キズナ</t>
-        </is>
-      </c>
-      <c r="B69" s="31" t="inlineStr">
-        <is>
-          <t>18頭: 中央勝ち上がり44%・回収≥1が22%・回収中央値0.11</t>
-        </is>
-      </c>
-      <c r="C69" s="31" t="inlineStr">
-        <is>
-          <t>重賞3頭</t>
-        </is>
-      </c>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>◆父の傾向（5年・中央400口・8頭以上）</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="inlineStr"/>
+      <c r="C69" s="31" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>エピファネイア</t>
+          <t>ニューイヤーズデイ</t>
         </is>
       </c>
       <c r="B70" s="31" t="inlineStr">
         <is>
-          <t>24頭: 中央勝ち上がり71%・回収≥1が21%・回収中央値0.38</t>
+          <t>10頭: 中央勝ち上がり90%・回収≥1が40%・回収中央値0.63</t>
         </is>
       </c>
       <c r="C70" s="31" t="inlineStr">
         <is>
-          <t>重賞1頭</t>
+          <t>重賞0頭</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>リオンディーズ</t>
+          <t>リアルスティール</t>
         </is>
       </c>
       <c r="B71" s="31" t="inlineStr">
         <is>
-          <t>10頭: 中央勝ち上がり50%・回収≥1が20%・回収中央値0.21</t>
+          <t>12頭: 中央勝ち上がり67%・回収≥1が33%・回収中央値0.39</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞2頭</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>ドゥラメンテ</t>
+          <t>ルーラーシップ</t>
         </is>
       </c>
       <c r="B72" s="31" t="inlineStr">
         <is>
-          <t>25頭: 中央勝ち上がり40%・回収≥1が20%・回収中央値0.08</t>
+          <t>15頭: 中央勝ち上がり47%・回収≥1が27%・回収中央値0.16</t>
         </is>
       </c>
       <c r="C72" s="31" t="inlineStr">
@@ -10110,12 +10098,12 @@
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>ロードカナロア</t>
+          <t>ハービンジャー</t>
         </is>
       </c>
       <c r="B73" s="31" t="inlineStr">
         <is>
-          <t>29頭: 中央勝ち上がり52%・回収≥1が17%・回収中央値0.15</t>
+          <t>16頭: 中央勝ち上がり44%・回収≥1が25%・回収中央値0.32</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
@@ -10127,29 +10115,29 @@
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>ハーツクライ</t>
+          <t>キズナ</t>
         </is>
       </c>
       <c r="B74" s="31" t="inlineStr">
         <is>
-          <t>12頭: 中央勝ち上がり42%・回収≥1が17%・回収中央値0.17</t>
+          <t>18頭: 中央勝ち上がり44%・回収≥1が22%・回収中央値0.11</t>
         </is>
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞3頭</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>モーリス</t>
+          <t>エピファネイア</t>
         </is>
       </c>
       <c r="B75" s="31" t="inlineStr">
         <is>
-          <t>32頭: 中央勝ち上がり59%・回収≥1が16%・回収中央値0.32</t>
+          <t>24頭: 中央勝ち上がり71%・回収≥1が21%・回収中央値0.38</t>
         </is>
       </c>
       <c r="C75" s="31" t="inlineStr">
@@ -10161,12 +10149,12 @@
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>サトノダイヤモンド</t>
+          <t>リオンディーズ</t>
         </is>
       </c>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>13頭: 中央勝ち上がり54%・回収≥1が15%・回収中央値0.28</t>
+          <t>10頭: 中央勝ち上がり50%・回収≥1が20%・回収中央値0.21</t>
         </is>
       </c>
       <c r="C76" s="31" t="inlineStr">
@@ -10178,46 +10166,46 @@
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>キタサンブラック</t>
+          <t>ドゥラメンテ</t>
         </is>
       </c>
       <c r="B77" s="31" t="inlineStr">
         <is>
-          <t>14頭: 中央勝ち上がり36%・回収≥1が14%・回収中央値0.13</t>
+          <t>25頭: 中央勝ち上がり40%・回収≥1が20%・回収中央値0.08</t>
         </is>
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>重賞2頭</t>
+          <t>重賞1頭</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>ドレフォン</t>
+          <t>ロードカナロア</t>
         </is>
       </c>
       <c r="B78" s="31" t="inlineStr">
         <is>
-          <t>22頭: 中央勝ち上がり32%・回収≥1が14%・回収中央値0.26</t>
+          <t>29頭: 中央勝ち上がり52%・回収≥1が17%・回収中央値0.15</t>
         </is>
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞2頭</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>ブリックスアンドモルタル</t>
+          <t>ハーツクライ</t>
         </is>
       </c>
       <c r="B79" s="31" t="inlineStr">
         <is>
-          <t>9頭: 中央勝ち上がり33%・回収≥1が11%・回収中央値0.08</t>
+          <t>12頭: 中央勝ち上がり42%・回収≥1が17%・回収中央値0.17</t>
         </is>
       </c>
       <c r="C79" s="31" t="inlineStr">
@@ -10229,29 +10217,29 @@
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>ミッキーアイル</t>
+          <t>モーリス</t>
         </is>
       </c>
       <c r="B80" s="31" t="inlineStr">
         <is>
-          <t>9頭: 中央勝ち上がり33%・回収≥1が11%・回収中央値0.27</t>
+          <t>32頭: 中央勝ち上がり59%・回収≥1が16%・回収中央値0.32</t>
         </is>
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
-          <t>重賞0頭</t>
+          <t>重賞1頭</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>ナダル</t>
+          <t>サトノダイヤモンド</t>
         </is>
       </c>
       <c r="B81" s="31" t="inlineStr">
         <is>
-          <t>10頭: 中央勝ち上がり70%・回収≥1が10%・回収中央値0.6</t>
+          <t>13頭: 中央勝ち上がり54%・回収≥1が15%・回収中央値0.28</t>
         </is>
       </c>
       <c r="C81" s="31" t="inlineStr">
@@ -10263,29 +10251,29 @@
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>サートゥルナーリア</t>
+          <t>キタサンブラック</t>
         </is>
       </c>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>13頭: 中央勝ち上がり23%・回収≥1が8%・回収中央値0.02</t>
+          <t>14頭: 中央勝ち上がり36%・回収≥1が14%・回収中央値0.13</t>
         </is>
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
-          <t>重賞1頭</t>
+          <t>重賞2頭</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
-          <t>シルバーステート</t>
+          <t>ドレフォン</t>
         </is>
       </c>
       <c r="B83" s="31" t="inlineStr">
         <is>
-          <t>8頭: 中央勝ち上がり62%・回収≥1が0%・回収中央値0.26</t>
+          <t>22頭: 中央勝ち上がり32%・回収≥1が14%・回収中央値0.26</t>
         </is>
       </c>
       <c r="C83" s="31" t="inlineStr">
@@ -10297,12 +10285,12 @@
     <row r="84">
       <c r="A84" s="31" t="inlineStr">
         <is>
-          <t>レイデオロ</t>
+          <t>ブリックスアンドモルタル</t>
         </is>
       </c>
       <c r="B84" s="31" t="inlineStr">
         <is>
-          <t>17頭: 中央勝ち上がり53%・回収≥1が0%・回収中央値0.22</t>
+          <t>9頭: 中央勝ち上がり33%・回収≥1が11%・回収中央値0.08</t>
         </is>
       </c>
       <c r="C84" s="31" t="inlineStr">
@@ -10314,61 +10302,146 @@
     <row r="85">
       <c r="A85" s="31" t="inlineStr">
         <is>
-          <t>※種牡馬の顔ぶれは毎年変わるため参考程度に</t>
-        </is>
-      </c>
-      <c r="B85" s="31" t="inlineStr"/>
-      <c r="C85" s="31" t="inlineStr"/>
+          <t>ミッキーアイル</t>
+        </is>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>9頭: 中央勝ち上がり33%・回収≥1が11%・回収中央値0.27</t>
+        </is>
+      </c>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="31" t="inlineStr"/>
-      <c r="B86" s="31" t="inlineStr"/>
-      <c r="C86" s="31" t="inlineStr"/>
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>ナダル</t>
+        </is>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>10頭: 中央勝ち上がり70%・回収≥1が10%・回収中央値0.6</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="inlineStr">
-        <is>
-          <t>◆注意</t>
-        </is>
-      </c>
-      <c r="B87" s="31" t="inlineStr"/>
-      <c r="C87" s="31" t="inlineStr"/>
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>サートゥルナーリア</t>
+        </is>
+      </c>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>13頭: 中央勝ち上がり23%・回収≥1が8%・回収中央値0.02</t>
+        </is>
+      </c>
+      <c r="C87" s="31" t="inlineStr">
+        <is>
+          <t>重賞1頭</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="31" t="inlineStr">
         <is>
-          <t>・2023年度募集は現4歳・2024年度募集は現3歳。回収率は今後上振れする</t>
-        </is>
-      </c>
-      <c r="B88" s="31" t="inlineStr"/>
-      <c r="C88" s="31" t="inlineStr"/>
+          <t>シルバーステート</t>
+        </is>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>8頭: 中央勝ち上がり62%・回収≥1が0%・回収中央値0.26</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="31" t="inlineStr">
         <is>
-          <t>・回収率は分母が募集価格なので、安い馬ほど高く出る。価格基準の効果にはその分が含まれる</t>
-        </is>
-      </c>
-      <c r="B89" s="31" t="inlineStr"/>
-      <c r="C89" s="31" t="inlineStr"/>
+          <t>レイデオロ</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="inlineStr">
+        <is>
+          <t>17頭: 中央勝ち上がり53%・回収≥1が0%・回収中央値0.22</t>
+        </is>
+      </c>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>重賞0頭</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="31" t="inlineStr">
         <is>
-          <t>・地方入厩予定馬（100口）21頭は中央で走らないため基準の導出から外している</t>
+          <t>※種牡馬の顔ぶれは毎年変わるため参考程度に</t>
         </is>
       </c>
       <c r="B90" s="31" t="inlineStr"/>
       <c r="C90" s="31" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="31" t="inlineStr">
-        <is>
-          <t>・メスは引退後の繁殖価値が回収に含まれていないため、実質はやや過小評価</t>
-        </is>
-      </c>
+      <c r="A91" s="31" t="inlineStr"/>
       <c r="B91" s="31" t="inlineStr"/>
       <c r="C91" s="31" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>◆注意</t>
+        </is>
+      </c>
+      <c r="B92" s="31" t="inlineStr"/>
+      <c r="C92" s="31" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="31" t="inlineStr">
+        <is>
+          <t>・2023年度募集は現4歳・2024年度募集は現3歳。回収率は今後上振れする</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="inlineStr"/>
+      <c r="C93" s="31" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="31" t="inlineStr">
+        <is>
+          <t>・回収率は分母が募集価格なので、安い馬ほど高く出る。価格基準の効果にはその分が含まれる</t>
+        </is>
+      </c>
+      <c r="B94" s="31" t="inlineStr"/>
+      <c r="C94" s="31" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>・地方入厩予定馬（100口）21頭は中央で走らないため基準の導出から外している</t>
+        </is>
+      </c>
+      <c r="B95" s="31" t="inlineStr"/>
+      <c r="C95" s="31" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="31" t="inlineStr">
+        <is>
+          <t>・メスは引退後の繁殖価値が回収に含まれていないため、実質はやや過小評価</t>
+        </is>
+      </c>
+      <c r="B96" s="31" t="inlineStr"/>
+      <c r="C96" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -15939,11 +16012,11 @@
         </is>
       </c>
       <c r="Y2" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z2" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -16035,11 +16108,11 @@
         </is>
       </c>
       <c r="Y3" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z3" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -16131,9 +16204,13 @@
         </is>
       </c>
       <c r="Y4" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="19">
       <c r="A5" s="31" t="n">
@@ -16223,11 +16300,11 @@
         </is>
       </c>
       <c r="Y5" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z5" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -16319,11 +16396,11 @@
         </is>
       </c>
       <c r="Y6" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -16415,11 +16492,11 @@
         </is>
       </c>
       <c r="Y7" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -16511,11 +16588,11 @@
         </is>
       </c>
       <c r="Y8" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -16607,11 +16684,11 @@
         </is>
       </c>
       <c r="Y9" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z9" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -16703,11 +16780,11 @@
         </is>
       </c>
       <c r="Y10" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z10" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -16799,11 +16876,11 @@
         </is>
       </c>
       <c r="Y11" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -16895,11 +16972,11 @@
         </is>
       </c>
       <c r="Y12" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z12" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -16991,11 +17068,11 @@
         </is>
       </c>
       <c r="Y13" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z13" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -17087,11 +17164,11 @@
         </is>
       </c>
       <c r="Y14" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z14" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -17183,11 +17260,11 @@
         </is>
       </c>
       <c r="Y15" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -17279,11 +17356,11 @@
         </is>
       </c>
       <c r="Y16" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z16" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -17755,11 +17832,11 @@
         </is>
       </c>
       <c r="Y21" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z21" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -17851,11 +17928,11 @@
         </is>
       </c>
       <c r="Y22" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z22" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -17947,11 +18024,11 @@
         </is>
       </c>
       <c r="Y23" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z23" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -18043,11 +18120,11 @@
         </is>
       </c>
       <c r="Y24" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z24" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -18139,11 +18216,11 @@
         </is>
       </c>
       <c r="Y25" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z25" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -18427,11 +18504,11 @@
         </is>
       </c>
       <c r="Y28" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z28" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -18811,11 +18888,11 @@
         </is>
       </c>
       <c r="Y32" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z32" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -19579,11 +19656,11 @@
         </is>
       </c>
       <c r="Y40" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z40" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -20055,11 +20132,11 @@
         </is>
       </c>
       <c r="Y45" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z45" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -20243,11 +20320,11 @@
         </is>
       </c>
       <c r="Y47" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z47" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -20339,9 +20416,13 @@
         </is>
       </c>
       <c r="Y48" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z48" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="19">
       <c r="A49" s="31" t="n">
@@ -20431,11 +20512,11 @@
         </is>
       </c>
       <c r="Y49" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -20527,11 +20608,11 @@
         </is>
       </c>
       <c r="Y50" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z50" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -20623,11 +20704,11 @@
         </is>
       </c>
       <c r="Y51" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z51" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -20719,11 +20800,11 @@
         </is>
       </c>
       <c r="Y52" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z52" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20896,11 @@
         </is>
       </c>
       <c r="Y53" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z53" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -20911,11 +20992,11 @@
         </is>
       </c>
       <c r="Y54" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z54" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -21007,11 +21088,11 @@
         </is>
       </c>
       <c r="Y55" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z55" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -21103,11 +21184,11 @@
         </is>
       </c>
       <c r="Y56" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z56" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -21199,11 +21280,11 @@
         </is>
       </c>
       <c r="Y57" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z57" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -21295,11 +21376,11 @@
         </is>
       </c>
       <c r="Y58" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z58" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -21391,11 +21472,11 @@
         </is>
       </c>
       <c r="Y59" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z59" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -21481,7 +21562,7 @@
       <c r="Y60" s="31" t="n"/>
       <c r="Z60" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -21573,11 +21654,11 @@
         </is>
       </c>
       <c r="Y61" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z61" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -21669,11 +21750,11 @@
         </is>
       </c>
       <c r="Y62" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z62" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -21745,11 +21826,11 @@
       </c>
       <c r="X63" s="31" t="inlineStr"/>
       <c r="Y63" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z63" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -21841,11 +21922,11 @@
         </is>
       </c>
       <c r="Y64" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z64" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -21937,11 +22018,11 @@
         </is>
       </c>
       <c r="Y65" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z65" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -22033,11 +22114,11 @@
         </is>
       </c>
       <c r="Y66" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z66" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -22129,11 +22210,11 @@
         </is>
       </c>
       <c r="Y67" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z67" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -22225,11 +22306,11 @@
         </is>
       </c>
       <c r="Y68" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z68" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -22321,11 +22402,11 @@
         </is>
       </c>
       <c r="Y69" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z69" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -22605,11 +22686,11 @@
         </is>
       </c>
       <c r="Y72" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z72" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -22701,11 +22782,11 @@
         </is>
       </c>
       <c r="Y73" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z73" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -23917,11 +23998,11 @@
         </is>
       </c>
       <c r="Y86" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z86" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -24677,11 +24758,11 @@
         </is>
       </c>
       <c r="Y94" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z94" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -24773,11 +24854,11 @@
         </is>
       </c>
       <c r="Y95" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z95" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -24869,11 +24950,11 @@
         </is>
       </c>
       <c r="Y96" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z96" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -24965,11 +25046,11 @@
         </is>
       </c>
       <c r="Y97" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z97" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25142,11 @@
         </is>
       </c>
       <c r="Y98" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z98" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -25157,11 +25238,11 @@
         </is>
       </c>
       <c r="Y99" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z99" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -25253,11 +25334,11 @@
         </is>
       </c>
       <c r="Y100" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z100" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -25541,11 +25622,11 @@
         </is>
       </c>
       <c r="Y103" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z103" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -25637,11 +25718,11 @@
         </is>
       </c>
       <c r="Y104" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z104" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -25733,11 +25814,11 @@
         </is>
       </c>
       <c r="Y105" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z105" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -25829,11 +25910,11 @@
         </is>
       </c>
       <c r="Y106" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z106" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -25925,11 +26006,11 @@
         </is>
       </c>
       <c r="Y107" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z107" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -26021,11 +26102,11 @@
         </is>
       </c>
       <c r="Y108" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z108" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -26117,11 +26198,11 @@
         </is>
       </c>
       <c r="Y109" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z109" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -26213,11 +26294,11 @@
         </is>
       </c>
       <c r="Y110" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z110" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -26405,11 +26486,11 @@
         </is>
       </c>
       <c r="Y112" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z112" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -26597,11 +26678,11 @@
         </is>
       </c>
       <c r="Y114" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z114" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -26693,11 +26774,11 @@
         </is>
       </c>
       <c r="Y115" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z115" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -26885,11 +26966,11 @@
         </is>
       </c>
       <c r="Y117" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z117" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -26981,11 +27062,11 @@
         </is>
       </c>
       <c r="Y118" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z118" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -27077,11 +27158,11 @@
         </is>
       </c>
       <c r="Y119" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z119" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -27173,11 +27254,11 @@
         </is>
       </c>
       <c r="Y120" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z120" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -27269,11 +27350,11 @@
         </is>
       </c>
       <c r="Y121" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z121" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -27365,11 +27446,11 @@
         </is>
       </c>
       <c r="Y122" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z122" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -27461,11 +27542,11 @@
         </is>
       </c>
       <c r="Y123" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z123" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -27557,11 +27638,11 @@
         </is>
       </c>
       <c r="Y124" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z124" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -27653,11 +27734,11 @@
         </is>
       </c>
       <c r="Y125" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z125" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -27749,11 +27830,11 @@
         </is>
       </c>
       <c r="Y126" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z126" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -27845,11 +27926,11 @@
         </is>
       </c>
       <c r="Y127" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z127" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -27941,11 +28022,11 @@
         </is>
       </c>
       <c r="Y128" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z128" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -28129,11 +28210,11 @@
         </is>
       </c>
       <c r="Y130" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z130" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -28321,11 +28402,11 @@
         </is>
       </c>
       <c r="Y132" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z132" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -28705,11 +28786,11 @@
         </is>
       </c>
       <c r="Y136" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z136" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -28801,11 +28882,11 @@
         </is>
       </c>
       <c r="Y137" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z137" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -28897,11 +28978,11 @@
         </is>
       </c>
       <c r="Y138" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z138" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -29089,11 +29170,11 @@
         </is>
       </c>
       <c r="Y140" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z140" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -29281,11 +29362,11 @@
         </is>
       </c>
       <c r="Y142" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z142" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -29473,11 +29554,11 @@
         </is>
       </c>
       <c r="Y144" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z144" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -30137,11 +30218,11 @@
         </is>
       </c>
       <c r="Y151" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z151" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -30233,11 +30314,11 @@
         </is>
       </c>
       <c r="Y152" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z152" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -30329,11 +30410,11 @@
         </is>
       </c>
       <c r="Y153" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z153" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -30425,11 +30506,11 @@
         </is>
       </c>
       <c r="Y154" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z154" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -30521,11 +30602,11 @@
         </is>
       </c>
       <c r="Y155" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z155" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -30617,11 +30698,11 @@
         </is>
       </c>
       <c r="Y156" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z156" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -30713,11 +30794,11 @@
         </is>
       </c>
       <c r="Y157" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z157" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -30901,11 +30982,11 @@
         </is>
       </c>
       <c r="Y159" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z159" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -31093,11 +31174,11 @@
         </is>
       </c>
       <c r="Y161" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z161" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -31189,11 +31270,11 @@
         </is>
       </c>
       <c r="Y162" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z162" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -31285,11 +31366,11 @@
         </is>
       </c>
       <c r="Y163" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z163" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -31473,11 +31554,11 @@
         </is>
       </c>
       <c r="Y165" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z165" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -31569,11 +31650,11 @@
         </is>
       </c>
       <c r="Y166" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z166" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -31665,11 +31746,11 @@
         </is>
       </c>
       <c r="Y167" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z167" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -31857,11 +31938,11 @@
         </is>
       </c>
       <c r="Y169" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z169" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -31953,11 +32034,11 @@
         </is>
       </c>
       <c r="Y170" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z170" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -32145,11 +32226,11 @@
         </is>
       </c>
       <c r="Y172" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z172" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -32433,11 +32514,11 @@
         </is>
       </c>
       <c r="Y175" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z175" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -32529,11 +32610,11 @@
         </is>
       </c>
       <c r="Y176" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z176" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -33005,11 +33086,11 @@
         </is>
       </c>
       <c r="Y181" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z181" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -33381,11 +33462,11 @@
         </is>
       </c>
       <c r="Y185" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z185" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -33477,11 +33558,11 @@
         </is>
       </c>
       <c r="Y186" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z186" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -33573,11 +33654,11 @@
         </is>
       </c>
       <c r="Y187" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z187" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -33669,11 +33750,11 @@
         </is>
       </c>
       <c r="Y188" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z188" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -33765,11 +33846,11 @@
         </is>
       </c>
       <c r="Y189" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z189" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -33861,11 +33942,11 @@
         </is>
       </c>
       <c r="Y190" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z190" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -33957,11 +34038,11 @@
         </is>
       </c>
       <c r="Y191" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z191" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -34053,11 +34134,11 @@
         </is>
       </c>
       <c r="Y192" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z192" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -34149,11 +34230,11 @@
         </is>
       </c>
       <c r="Y193" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z193" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -34245,11 +34326,11 @@
         </is>
       </c>
       <c r="Y194" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z194" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -34341,11 +34422,11 @@
         </is>
       </c>
       <c r="Y195" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z195" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -34437,11 +34518,11 @@
         </is>
       </c>
       <c r="Y196" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z196" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -34629,11 +34710,11 @@
         </is>
       </c>
       <c r="Y198" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z198" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -34725,11 +34806,11 @@
         </is>
       </c>
       <c r="Y199" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z199" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -34821,11 +34902,11 @@
         </is>
       </c>
       <c r="Y200" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z200" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -35105,11 +35186,11 @@
         </is>
       </c>
       <c r="Y203" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z203" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -35201,11 +35282,11 @@
         </is>
       </c>
       <c r="Y204" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z204" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -35581,11 +35662,11 @@
         </is>
       </c>
       <c r="Y208" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z208" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -35769,11 +35850,11 @@
         </is>
       </c>
       <c r="Y210" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z210" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -35865,11 +35946,11 @@
         </is>
       </c>
       <c r="Y211" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z211" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -36153,11 +36234,11 @@
         </is>
       </c>
       <c r="Y214" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z214" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -36249,9 +36330,13 @@
         </is>
       </c>
       <c r="Y215" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z215" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z215" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="15" customHeight="1" s="19">
       <c r="A216" s="31" t="n">
@@ -36437,11 +36522,11 @@
         </is>
       </c>
       <c r="Y217" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z217" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -36629,11 +36714,11 @@
         </is>
       </c>
       <c r="Y219" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z219" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -36817,11 +36902,11 @@
         </is>
       </c>
       <c r="Y221" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z221" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -37009,11 +37094,11 @@
         </is>
       </c>
       <c r="Y223" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z223" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -37197,11 +37282,11 @@
         </is>
       </c>
       <c r="Y225" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z225" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -37293,11 +37378,11 @@
         </is>
       </c>
       <c r="Y226" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z226" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -37389,11 +37474,11 @@
         </is>
       </c>
       <c r="Y227" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z227" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -37485,11 +37570,11 @@
         </is>
       </c>
       <c r="Y228" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z228" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -37581,11 +37666,11 @@
         </is>
       </c>
       <c r="Y229" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z229" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -37869,11 +37954,11 @@
         </is>
       </c>
       <c r="Y232" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z232" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -37965,11 +38050,11 @@
         </is>
       </c>
       <c r="Y233" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z233" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38061,9 +38146,13 @@
         </is>
       </c>
       <c r="Y234" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z234" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z234" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1" s="19">
       <c r="A235" s="31" t="n">
@@ -38153,11 +38242,11 @@
         </is>
       </c>
       <c r="Y235" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z235" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38249,11 +38338,11 @@
         </is>
       </c>
       <c r="Y236" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z236" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38345,11 +38434,11 @@
         </is>
       </c>
       <c r="Y237" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z237" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38441,11 +38530,11 @@
         </is>
       </c>
       <c r="Y238" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z238" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38537,11 +38626,11 @@
         </is>
       </c>
       <c r="Y239" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z239" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38633,11 +38722,11 @@
         </is>
       </c>
       <c r="Y240" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z240" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38729,11 +38818,11 @@
         </is>
       </c>
       <c r="Y241" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z241" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -38825,11 +38914,11 @@
         </is>
       </c>
       <c r="Y242" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z242" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -38921,9 +39010,13 @@
         </is>
       </c>
       <c r="Y243" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z243" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z243" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="15" customHeight="1" s="19">
       <c r="A244" s="31" t="n">
@@ -39013,11 +39106,11 @@
         </is>
       </c>
       <c r="Y244" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z244" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -39109,11 +39202,11 @@
         </is>
       </c>
       <c r="Y245" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z245" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -39205,11 +39298,11 @@
         </is>
       </c>
       <c r="Y246" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z246" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -39301,11 +39394,11 @@
         </is>
       </c>
       <c r="Y247" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z247" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -39397,11 +39490,11 @@
         </is>
       </c>
       <c r="Y248" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z248" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -39493,11 +39586,11 @@
         </is>
       </c>
       <c r="Y249" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z249" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -39589,11 +39682,11 @@
         </is>
       </c>
       <c r="Y250" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z250" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -39781,11 +39874,11 @@
         </is>
       </c>
       <c r="Y252" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z252" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -39877,11 +39970,11 @@
         </is>
       </c>
       <c r="Y253" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z253" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -39973,11 +40066,11 @@
         </is>
       </c>
       <c r="Y254" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z254" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -40069,11 +40162,11 @@
         </is>
       </c>
       <c r="Y255" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z255" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -40257,11 +40350,11 @@
         </is>
       </c>
       <c r="Y257" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z257" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -40353,11 +40446,11 @@
         </is>
       </c>
       <c r="Y258" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z258" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -40449,11 +40542,11 @@
         </is>
       </c>
       <c r="Y259" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z259" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -40545,11 +40638,11 @@
         </is>
       </c>
       <c r="Y260" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z260" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -40641,11 +40734,11 @@
         </is>
       </c>
       <c r="Y261" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z261" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -40737,11 +40830,11 @@
         </is>
       </c>
       <c r="Y262" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z262" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -40925,11 +41018,11 @@
         </is>
       </c>
       <c r="Y264" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z264" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -41117,11 +41210,11 @@
         </is>
       </c>
       <c r="Y266" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z266" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -41213,11 +41306,11 @@
         </is>
       </c>
       <c r="Y267" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z267" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -41309,11 +41402,11 @@
         </is>
       </c>
       <c r="Y268" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z268" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -41405,11 +41498,11 @@
         </is>
       </c>
       <c r="Y269" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z269" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -41501,11 +41594,11 @@
         </is>
       </c>
       <c r="Y270" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z270" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -41693,11 +41786,11 @@
         </is>
       </c>
       <c r="Y272" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z272" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -42210,9 +42303,7 @@
       <c r="H278" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I278" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I278" s="31" t="n"/>
       <c r="J278" s="31" t="n">
         <v>7000</v>
       </c>
@@ -42265,11 +42356,11 @@
         </is>
       </c>
       <c r="Y278" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z278" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -42306,9 +42397,7 @@
       <c r="H279" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I279" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I279" s="31" t="n"/>
       <c r="J279" s="31" t="n">
         <v>5000</v>
       </c>
@@ -42361,11 +42450,11 @@
         </is>
       </c>
       <c r="Y279" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z279" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -42402,9 +42491,7 @@
       <c r="H280" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I280" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I280" s="31" t="n"/>
       <c r="J280" s="31" t="n">
         <v>5000</v>
       </c>
@@ -42457,11 +42544,11 @@
         </is>
       </c>
       <c r="Y280" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z280" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -42498,9 +42585,7 @@
       <c r="H281" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I281" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I281" s="31" t="n"/>
       <c r="J281" s="31" t="n">
         <v>7000</v>
       </c>
@@ -42553,9 +42638,13 @@
         </is>
       </c>
       <c r="Y281" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z281" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z281" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="31" t="n">
@@ -42590,9 +42679,7 @@
       <c r="H282" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I282" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I282" s="31" t="n"/>
       <c r="J282" s="31" t="n">
         <v>6000</v>
       </c>
@@ -42645,11 +42732,11 @@
         </is>
       </c>
       <c r="Y282" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z282" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -42686,9 +42773,7 @@
       <c r="H283" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I283" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I283" s="31" t="n"/>
       <c r="J283" s="31" t="n">
         <v>5000</v>
       </c>
@@ -42741,11 +42826,11 @@
         </is>
       </c>
       <c r="Y283" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z283" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -42782,9 +42867,7 @@
       <c r="H284" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I284" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I284" s="31" t="n"/>
       <c r="J284" s="31" t="n">
         <v>8000</v>
       </c>
@@ -42837,11 +42920,11 @@
         </is>
       </c>
       <c r="Y284" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z284" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -42878,9 +42961,7 @@
       <c r="H285" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I285" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I285" s="31" t="n"/>
       <c r="J285" s="31" t="n">
         <v>4000</v>
       </c>
@@ -42933,9 +43014,13 @@
         </is>
       </c>
       <c r="Y285" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z285" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z285" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="31" t="n">
@@ -42970,9 +43055,7 @@
       <c r="H286" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I286" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I286" s="31" t="n"/>
       <c r="J286" s="31" t="n">
         <v>3600</v>
       </c>
@@ -43025,11 +43108,11 @@
         </is>
       </c>
       <c r="Y286" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z286" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -43066,9 +43149,7 @@
       <c r="H287" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I287" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I287" s="31" t="n"/>
       <c r="J287" s="31" t="n">
         <v>7000</v>
       </c>
@@ -43121,11 +43202,11 @@
         </is>
       </c>
       <c r="Y287" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z287" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -43162,9 +43243,7 @@
       <c r="H288" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I288" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I288" s="31" t="n"/>
       <c r="J288" s="31" t="n">
         <v>2400</v>
       </c>
@@ -43254,9 +43333,7 @@
       <c r="H289" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I289" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I289" s="31" t="n"/>
       <c r="J289" s="31" t="n">
         <v>5000</v>
       </c>
@@ -43309,11 +43386,11 @@
         </is>
       </c>
       <c r="Y289" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z289" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -43350,9 +43427,7 @@
       <c r="H290" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I290" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I290" s="31" t="n"/>
       <c r="J290" s="31" t="n">
         <v>4000</v>
       </c>
@@ -43405,11 +43480,11 @@
         </is>
       </c>
       <c r="Y290" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z290" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -43446,9 +43521,7 @@
       <c r="H291" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I291" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I291" s="31" t="n"/>
       <c r="J291" s="31" t="n">
         <v>5000</v>
       </c>
@@ -43501,9 +43574,13 @@
         </is>
       </c>
       <c r="Y291" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z291" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z291" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="31" t="n">
@@ -43538,9 +43615,7 @@
       <c r="H292" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I292" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I292" s="31" t="n"/>
       <c r="J292" s="31" t="n">
         <v>5000</v>
       </c>
@@ -43593,11 +43668,11 @@
         </is>
       </c>
       <c r="Y292" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z292" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -43634,9 +43709,7 @@
       <c r="H293" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I293" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I293" s="31" t="n"/>
       <c r="J293" s="31" t="n">
         <v>3200</v>
       </c>
@@ -43689,11 +43762,11 @@
         </is>
       </c>
       <c r="Y293" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z293" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -43730,9 +43803,7 @@
       <c r="H294" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I294" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I294" s="31" t="n"/>
       <c r="J294" s="31" t="n">
         <v>4000</v>
       </c>
@@ -43785,11 +43856,11 @@
         </is>
       </c>
       <c r="Y294" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z294" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -43826,9 +43897,7 @@
       <c r="H295" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I295" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I295" s="31" t="n"/>
       <c r="J295" s="31" t="n">
         <v>4000</v>
       </c>
@@ -43881,11 +43950,11 @@
         </is>
       </c>
       <c r="Y295" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z295" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -43922,9 +43991,7 @@
       <c r="H296" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I296" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I296" s="31" t="n"/>
       <c r="J296" s="31" t="n">
         <v>3600</v>
       </c>
@@ -43977,11 +44044,11 @@
         </is>
       </c>
       <c r="Y296" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z296" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -44018,9 +44085,7 @@
       <c r="H297" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I297" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I297" s="31" t="n"/>
       <c r="J297" s="31" t="n">
         <v>3600</v>
       </c>
@@ -44073,11 +44138,11 @@
         </is>
       </c>
       <c r="Y297" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z297" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -44114,9 +44179,7 @@
       <c r="H298" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I298" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I298" s="31" t="n"/>
       <c r="J298" s="31" t="n">
         <v>4000</v>
       </c>
@@ -44169,11 +44232,11 @@
         </is>
       </c>
       <c r="Y298" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z298" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -44210,9 +44273,7 @@
       <c r="H299" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I299" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I299" s="31" t="n"/>
       <c r="J299" s="31" t="n">
         <v>2400</v>
       </c>
@@ -44306,9 +44367,7 @@
       <c r="H300" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I300" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I300" s="31" t="n"/>
       <c r="J300" s="31" t="n">
         <v>5000</v>
       </c>
@@ -44361,11 +44420,11 @@
         </is>
       </c>
       <c r="Y300" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z300" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -44402,9 +44461,7 @@
       <c r="H301" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I301" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I301" s="31" t="n"/>
       <c r="J301" s="31" t="n">
         <v>2400</v>
       </c>
@@ -44498,9 +44555,7 @@
       <c r="H302" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I302" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I302" s="31" t="n"/>
       <c r="J302" s="31" t="n">
         <v>3200</v>
       </c>
@@ -44553,11 +44608,11 @@
         </is>
       </c>
       <c r="Y302" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z302" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -44594,9 +44649,7 @@
       <c r="H303" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I303" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I303" s="31" t="n"/>
       <c r="J303" s="31" t="n">
         <v>3000</v>
       </c>
@@ -44649,11 +44702,11 @@
         </is>
       </c>
       <c r="Y303" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z303" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -44690,9 +44743,7 @@
       <c r="H304" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I304" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I304" s="31" t="n"/>
       <c r="J304" s="31" t="n">
         <v>3200</v>
       </c>
@@ -44745,11 +44796,11 @@
         </is>
       </c>
       <c r="Y304" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z304" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -44786,9 +44837,7 @@
       <c r="H305" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I305" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I305" s="31" t="n"/>
       <c r="J305" s="31" t="n">
         <v>3000</v>
       </c>
@@ -44841,11 +44890,11 @@
         </is>
       </c>
       <c r="Y305" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z305" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -44882,9 +44931,7 @@
       <c r="H306" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I306" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I306" s="31" t="n"/>
       <c r="J306" s="31" t="n">
         <v>2400</v>
       </c>
@@ -44978,9 +45025,7 @@
       <c r="H307" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I307" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I307" s="31" t="n"/>
       <c r="J307" s="31" t="n">
         <v>2000</v>
       </c>
@@ -45074,9 +45119,7 @@
       <c r="H308" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I308" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I308" s="31" t="n"/>
       <c r="J308" s="31" t="n">
         <v>2800</v>
       </c>
@@ -45129,11 +45172,11 @@
         </is>
       </c>
       <c r="Y308" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z308" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -45170,9 +45213,7 @@
       <c r="H309" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I309" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I309" s="31" t="n"/>
       <c r="J309" s="31" t="n">
         <v>4000</v>
       </c>
@@ -45225,11 +45266,11 @@
         </is>
       </c>
       <c r="Y309" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z309" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -45266,9 +45307,7 @@
       <c r="H310" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I310" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I310" s="31" t="n"/>
       <c r="J310" s="31" t="n">
         <v>2800</v>
       </c>
@@ -45321,11 +45360,11 @@
         </is>
       </c>
       <c r="Y310" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z310" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -45362,9 +45401,7 @@
       <c r="H311" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I311" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I311" s="31" t="n"/>
       <c r="J311" s="31" t="n">
         <v>3600</v>
       </c>
@@ -45417,11 +45454,11 @@
         </is>
       </c>
       <c r="Y311" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z311" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -45458,9 +45495,7 @@
       <c r="H312" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I312" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I312" s="31" t="n"/>
       <c r="J312" s="31" t="n">
         <v>2400</v>
       </c>
@@ -45550,9 +45585,7 @@
       <c r="H313" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="I313" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I313" s="31" t="n"/>
       <c r="J313" s="31" t="n">
         <v>2400</v>
       </c>
@@ -45646,9 +45679,7 @@
       <c r="H314" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I314" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I314" s="31" t="n"/>
       <c r="J314" s="31" t="n">
         <v>1800</v>
       </c>
@@ -45742,9 +45773,7 @@
       <c r="H315" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I315" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I315" s="31" t="n"/>
       <c r="J315" s="31" t="n">
         <v>6000</v>
       </c>
@@ -45797,9 +45826,13 @@
         </is>
       </c>
       <c r="Y315" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z315" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z315" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="31" t="n">
@@ -45834,9 +45867,7 @@
       <c r="H316" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="I316" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I316" s="31" t="n"/>
       <c r="J316" s="31" t="n">
         <v>3200</v>
       </c>
@@ -45889,11 +45920,11 @@
         </is>
       </c>
       <c r="Y316" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z316" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -45930,9 +45961,7 @@
       <c r="H317" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I317" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I317" s="31" t="n"/>
       <c r="J317" s="31" t="n">
         <v>2600</v>
       </c>
@@ -45985,11 +46014,11 @@
         </is>
       </c>
       <c r="Y317" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z317" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -46026,9 +46055,7 @@
       <c r="H318" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I318" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I318" s="31" t="n"/>
       <c r="J318" s="31" t="n">
         <v>3200</v>
       </c>
@@ -46081,11 +46108,11 @@
         </is>
       </c>
       <c r="Y318" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z318" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -46122,9 +46149,7 @@
       <c r="H319" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I319" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I319" s="31" t="n"/>
       <c r="J319" s="31" t="n">
         <v>2400</v>
       </c>
@@ -46218,9 +46243,7 @@
       <c r="H320" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I320" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I320" s="31" t="n"/>
       <c r="J320" s="31" t="n">
         <v>3200</v>
       </c>
@@ -46273,11 +46296,11 @@
         </is>
       </c>
       <c r="Y320" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z320" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -46314,9 +46337,7 @@
       <c r="H321" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I321" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I321" s="31" t="n"/>
       <c r="J321" s="31" t="n">
         <v>2600</v>
       </c>
@@ -46369,11 +46390,11 @@
         </is>
       </c>
       <c r="Y321" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z321" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -46410,9 +46431,7 @@
       <c r="H322" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="I322" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I322" s="31" t="n"/>
       <c r="J322" s="31" t="n">
         <v>3000</v>
       </c>
@@ -46465,11 +46484,11 @@
         </is>
       </c>
       <c r="Y322" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z322" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -46506,9 +46525,7 @@
       <c r="H323" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I323" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I323" s="31" t="n"/>
       <c r="J323" s="31" t="n">
         <v>3600</v>
       </c>
@@ -46561,11 +46578,11 @@
         </is>
       </c>
       <c r="Y323" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z323" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -46602,9 +46619,7 @@
       <c r="H324" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I324" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I324" s="31" t="n"/>
       <c r="J324" s="31" t="n">
         <v>4000</v>
       </c>
@@ -46657,11 +46672,11 @@
         </is>
       </c>
       <c r="Y324" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z324" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -46698,9 +46713,7 @@
       <c r="H325" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I325" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I325" s="31" t="n"/>
       <c r="J325" s="31" t="n">
         <v>5000</v>
       </c>
@@ -46753,11 +46766,11 @@
         </is>
       </c>
       <c r="Y325" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z325" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -46794,9 +46807,7 @@
       <c r="H326" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I326" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I326" s="31" t="n"/>
       <c r="J326" s="31" t="n">
         <v>3600</v>
       </c>
@@ -46849,11 +46860,11 @@
         </is>
       </c>
       <c r="Y326" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z326" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -46890,9 +46901,7 @@
       <c r="H327" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I327" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I327" s="31" t="n"/>
       <c r="J327" s="31" t="n">
         <v>5000</v>
       </c>
@@ -46945,11 +46954,11 @@
         </is>
       </c>
       <c r="Y327" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z327" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -46986,9 +46995,7 @@
       <c r="H328" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I328" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I328" s="31" t="n"/>
       <c r="J328" s="31" t="n">
         <v>4200</v>
       </c>
@@ -47041,11 +47048,11 @@
         </is>
       </c>
       <c r="Y328" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z328" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47082,9 +47089,7 @@
       <c r="H329" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I329" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I329" s="31" t="n"/>
       <c r="J329" s="31" t="n">
         <v>6000</v>
       </c>
@@ -47137,11 +47142,11 @@
         </is>
       </c>
       <c r="Y329" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z329" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47178,9 +47183,7 @@
       <c r="H330" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I330" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I330" s="31" t="n"/>
       <c r="J330" s="31" t="n">
         <v>3600</v>
       </c>
@@ -47233,11 +47236,11 @@
         </is>
       </c>
       <c r="Y330" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z330" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -47274,9 +47277,7 @@
       <c r="H331" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I331" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I331" s="31" t="n"/>
       <c r="J331" s="31" t="n">
         <v>6000</v>
       </c>
@@ -47329,11 +47330,11 @@
         </is>
       </c>
       <c r="Y331" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z331" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47370,9 +47371,7 @@
       <c r="H332" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I332" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I332" s="31" t="n"/>
       <c r="J332" s="31" t="n">
         <v>4000</v>
       </c>
@@ -47425,11 +47424,11 @@
         </is>
       </c>
       <c r="Y332" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z332" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47466,9 +47465,7 @@
       <c r="H333" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I333" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I333" s="31" t="n"/>
       <c r="J333" s="31" t="n">
         <v>12000</v>
       </c>
@@ -47521,11 +47518,11 @@
         </is>
       </c>
       <c r="Y333" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z333" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47562,9 +47559,7 @@
       <c r="H334" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I334" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I334" s="31" t="n"/>
       <c r="J334" s="31" t="n">
         <v>5000</v>
       </c>
@@ -47617,11 +47612,11 @@
         </is>
       </c>
       <c r="Y334" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z334" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47658,9 +47653,7 @@
       <c r="H335" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I335" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I335" s="31" t="n"/>
       <c r="J335" s="31" t="n">
         <v>6000</v>
       </c>
@@ -47713,11 +47706,11 @@
         </is>
       </c>
       <c r="Y335" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z335" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47754,9 +47747,7 @@
       <c r="H336" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I336" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I336" s="31" t="n"/>
       <c r="J336" s="31" t="n">
         <v>6000</v>
       </c>
@@ -47809,11 +47800,11 @@
         </is>
       </c>
       <c r="Y336" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z336" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47850,9 +47841,7 @@
       <c r="H337" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I337" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I337" s="31" t="n"/>
       <c r="J337" s="31" t="n">
         <v>6000</v>
       </c>
@@ -47905,11 +47894,11 @@
         </is>
       </c>
       <c r="Y337" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z337" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -47946,9 +47935,7 @@
       <c r="H338" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I338" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I338" s="31" t="n"/>
       <c r="J338" s="31" t="n">
         <v>7000</v>
       </c>
@@ -48001,11 +47988,11 @@
         </is>
       </c>
       <c r="Y338" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z338" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -48042,9 +48029,7 @@
       <c r="H339" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I339" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I339" s="31" t="n"/>
       <c r="J339" s="31" t="n">
         <v>4600</v>
       </c>
@@ -48097,11 +48082,11 @@
         </is>
       </c>
       <c r="Y339" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z339" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -48138,9 +48123,7 @@
       <c r="H340" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I340" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I340" s="31" t="n"/>
       <c r="J340" s="31" t="n">
         <v>4000</v>
       </c>
@@ -48193,11 +48176,11 @@
         </is>
       </c>
       <c r="Y340" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z340" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -48234,9 +48217,7 @@
       <c r="H341" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I341" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I341" s="31" t="n"/>
       <c r="J341" s="31" t="n">
         <v>3600</v>
       </c>
@@ -48289,11 +48270,11 @@
         </is>
       </c>
       <c r="Y341" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z341" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -48330,9 +48311,7 @@
       <c r="H342" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I342" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I342" s="31" t="n"/>
       <c r="J342" s="31" t="n">
         <v>3000</v>
       </c>
@@ -48385,11 +48364,11 @@
         </is>
       </c>
       <c r="Y342" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z342" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -48426,9 +48405,7 @@
       <c r="H343" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I343" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I343" s="31" t="n"/>
       <c r="J343" s="31" t="n">
         <v>3000</v>
       </c>
@@ -48481,11 +48458,11 @@
         </is>
       </c>
       <c r="Y343" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z343" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -48522,9 +48499,7 @@
       <c r="H344" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I344" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I344" s="31" t="n"/>
       <c r="J344" s="31" t="n">
         <v>4000</v>
       </c>
@@ -48577,9 +48552,13 @@
         </is>
       </c>
       <c r="Y344" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z344" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z344" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="31" t="n">
@@ -48614,9 +48593,7 @@
       <c r="H345" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I345" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I345" s="31" t="n"/>
       <c r="J345" s="31" t="n">
         <v>3600</v>
       </c>
@@ -48669,11 +48646,11 @@
         </is>
       </c>
       <c r="Y345" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z345" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -48710,9 +48687,7 @@
       <c r="H346" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I346" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I346" s="31" t="n"/>
       <c r="J346" s="31" t="n">
         <v>3000</v>
       </c>
@@ -48765,11 +48740,11 @@
         </is>
       </c>
       <c r="Y346" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z346" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -48806,9 +48781,7 @@
       <c r="H347" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I347" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I347" s="31" t="n"/>
       <c r="J347" s="31" t="n">
         <v>2800</v>
       </c>
@@ -48861,11 +48834,11 @@
         </is>
       </c>
       <c r="Y347" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z347" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -48902,9 +48875,7 @@
       <c r="H348" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I348" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I348" s="31" t="n"/>
       <c r="J348" s="31" t="n">
         <v>2800</v>
       </c>
@@ -48957,11 +48928,11 @@
         </is>
       </c>
       <c r="Y348" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z348" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -48998,9 +48969,7 @@
       <c r="H349" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I349" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I349" s="31" t="n"/>
       <c r="J349" s="31" t="n">
         <v>2600</v>
       </c>
@@ -49053,11 +49022,11 @@
         </is>
       </c>
       <c r="Y349" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z349" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -49094,9 +49063,7 @@
       <c r="H350" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I350" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I350" s="31" t="n"/>
       <c r="J350" s="31" t="n">
         <v>4000</v>
       </c>
@@ -49149,11 +49116,11 @@
         </is>
       </c>
       <c r="Y350" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z350" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -49190,9 +49157,7 @@
       <c r="H351" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="I351" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I351" s="31" t="n"/>
       <c r="J351" s="31" t="n">
         <v>3000</v>
       </c>
@@ -49245,11 +49210,11 @@
         </is>
       </c>
       <c r="Y351" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z351" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -49286,9 +49251,7 @@
       <c r="H352" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I352" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I352" s="31" t="n"/>
       <c r="J352" s="31" t="n">
         <v>5000</v>
       </c>
@@ -49341,11 +49304,11 @@
         </is>
       </c>
       <c r="Y352" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z352" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -49382,9 +49345,7 @@
       <c r="H353" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I353" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I353" s="31" t="n"/>
       <c r="J353" s="31" t="n">
         <v>3200</v>
       </c>
@@ -49437,11 +49398,11 @@
         </is>
       </c>
       <c r="Y353" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z353" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -49478,9 +49439,7 @@
       <c r="H354" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I354" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I354" s="31" t="n"/>
       <c r="J354" s="31" t="n">
         <v>3600</v>
       </c>
@@ -49533,11 +49492,11 @@
         </is>
       </c>
       <c r="Y354" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z354" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -49574,9 +49533,7 @@
       <c r="H355" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I355" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I355" s="31" t="n"/>
       <c r="J355" s="31" t="n">
         <v>3000</v>
       </c>
@@ -49629,11 +49586,11 @@
         </is>
       </c>
       <c r="Y355" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z355" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -49670,9 +49627,7 @@
       <c r="H356" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I356" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I356" s="31" t="n"/>
       <c r="J356" s="31" t="n">
         <v>2400</v>
       </c>
@@ -49766,9 +49721,7 @@
       <c r="H357" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I357" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I357" s="31" t="n"/>
       <c r="J357" s="31" t="n">
         <v>2400</v>
       </c>
@@ -49862,9 +49815,7 @@
       <c r="H358" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I358" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I358" s="31" t="n"/>
       <c r="J358" s="31" t="n">
         <v>2400</v>
       </c>
@@ -49958,9 +49909,7 @@
       <c r="H359" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I359" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I359" s="31" t="n"/>
       <c r="J359" s="31" t="n">
         <v>2800</v>
       </c>
@@ -50013,11 +49962,11 @@
         </is>
       </c>
       <c r="Y359" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z359" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50054,9 +50003,7 @@
       <c r="H360" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I360" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I360" s="31" t="n"/>
       <c r="J360" s="31" t="n">
         <v>2600</v>
       </c>
@@ -50109,11 +50056,11 @@
         </is>
       </c>
       <c r="Y360" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z360" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50150,9 +50097,7 @@
       <c r="H361" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I361" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I361" s="31" t="n"/>
       <c r="J361" s="31" t="n">
         <v>2800</v>
       </c>
@@ -50205,11 +50150,11 @@
         </is>
       </c>
       <c r="Y361" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z361" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50246,9 +50191,7 @@
       <c r="H362" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I362" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I362" s="31" t="n"/>
       <c r="J362" s="31" t="n">
         <v>3600</v>
       </c>
@@ -50301,11 +50244,11 @@
         </is>
       </c>
       <c r="Y362" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z362" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50342,9 +50285,7 @@
       <c r="H363" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="I363" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I363" s="31" t="n"/>
       <c r="J363" s="31" t="n">
         <v>3000</v>
       </c>
@@ -50397,11 +50338,11 @@
         </is>
       </c>
       <c r="Y363" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z363" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50438,9 +50379,7 @@
       <c r="H364" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I364" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I364" s="31" t="n"/>
       <c r="J364" s="31" t="n">
         <v>3000</v>
       </c>
@@ -50493,11 +50432,11 @@
         </is>
       </c>
       <c r="Y364" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z364" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -50534,9 +50473,7 @@
       <c r="H365" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I365" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I365" s="31" t="n"/>
       <c r="J365" s="31" t="n">
         <v>3600</v>
       </c>
@@ -50589,11 +50526,11 @@
         </is>
       </c>
       <c r="Y365" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z365" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50630,9 +50567,7 @@
       <c r="H366" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I366" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I366" s="31" t="n"/>
       <c r="J366" s="31" t="n">
         <v>3000</v>
       </c>
@@ -50685,11 +50620,11 @@
         </is>
       </c>
       <c r="Y366" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z366" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -50726,9 +50661,7 @@
       <c r="H367" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I367" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I367" s="31" t="n"/>
       <c r="J367" s="31" t="n">
         <v>5000</v>
       </c>
@@ -50781,11 +50714,11 @@
         </is>
       </c>
       <c r="Y367" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z367" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -50822,9 +50755,7 @@
       <c r="H368" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I368" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I368" s="31" t="n"/>
       <c r="J368" s="31" t="n">
         <v>4400</v>
       </c>
@@ -50877,11 +50808,11 @@
         </is>
       </c>
       <c r="Y368" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z368" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -50918,9 +50849,7 @@
       <c r="H369" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I369" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I369" s="31" t="n"/>
       <c r="J369" s="31" t="n">
         <v>1800</v>
       </c>
@@ -51014,9 +50943,7 @@
       <c r="H370" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="I370" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I370" s="31" t="n"/>
       <c r="J370" s="31" t="n">
         <v>1800</v>
       </c>
@@ -51110,9 +51037,7 @@
       <c r="H371" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I371" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I371" s="31" t="n"/>
       <c r="J371" s="31" t="n">
         <v>2000</v>
       </c>
@@ -51206,9 +51131,7 @@
       <c r="H372" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I372" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I372" s="31" t="n"/>
       <c r="J372" s="31" t="n">
         <v>2000</v>
       </c>
@@ -51302,9 +51225,7 @@
       <c r="H373" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I373" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I373" s="31" t="n"/>
       <c r="J373" s="31" t="n">
         <v>5000</v>
       </c>
@@ -51357,11 +51278,11 @@
         </is>
       </c>
       <c r="Y373" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z373" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51398,9 +51319,7 @@
       <c r="H374" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I374" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I374" s="31" t="n"/>
       <c r="J374" s="31" t="n">
         <v>7000</v>
       </c>
@@ -51453,11 +51372,11 @@
         </is>
       </c>
       <c r="Y374" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z374" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51494,9 +51413,7 @@
       <c r="H375" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I375" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I375" s="31" t="n"/>
       <c r="J375" s="31" t="n">
         <v>7000</v>
       </c>
@@ -51549,11 +51466,11 @@
         </is>
       </c>
       <c r="Y375" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z375" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51590,9 +51507,7 @@
       <c r="H376" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I376" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I376" s="31" t="n"/>
       <c r="J376" s="31" t="n">
         <v>5000</v>
       </c>
@@ -51645,11 +51560,11 @@
         </is>
       </c>
       <c r="Y376" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z376" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51686,9 +51601,7 @@
       <c r="H377" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I377" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I377" s="31" t="n"/>
       <c r="J377" s="31" t="n">
         <v>8000</v>
       </c>
@@ -51741,11 +51654,11 @@
         </is>
       </c>
       <c r="Y377" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z377" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51782,9 +51695,7 @@
       <c r="H378" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I378" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I378" s="31" t="n"/>
       <c r="J378" s="31" t="n">
         <v>5000</v>
       </c>
@@ -51837,11 +51748,11 @@
         </is>
       </c>
       <c r="Y378" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z378" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51878,9 +51789,7 @@
       <c r="H379" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I379" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I379" s="31" t="n"/>
       <c r="J379" s="31" t="n">
         <v>8000</v>
       </c>
@@ -51933,11 +51842,11 @@
         </is>
       </c>
       <c r="Y379" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z379" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -51974,9 +51883,7 @@
       <c r="H380" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I380" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I380" s="31" t="n"/>
       <c r="J380" s="31" t="n">
         <v>7000</v>
       </c>
@@ -52029,11 +51936,11 @@
         </is>
       </c>
       <c r="Y380" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z380" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52070,9 +51977,7 @@
       <c r="H381" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I381" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I381" s="31" t="n"/>
       <c r="J381" s="31" t="n">
         <v>10000</v>
       </c>
@@ -52125,11 +52030,11 @@
         </is>
       </c>
       <c r="Y381" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z381" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52166,9 +52071,7 @@
       <c r="H382" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I382" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I382" s="31" t="n"/>
       <c r="J382" s="31" t="n">
         <v>6000</v>
       </c>
@@ -52221,11 +52124,11 @@
         </is>
       </c>
       <c r="Y382" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z382" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52262,9 +52165,7 @@
       <c r="H383" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I383" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I383" s="31" t="n"/>
       <c r="J383" s="31" t="n">
         <v>5000</v>
       </c>
@@ -52317,11 +52218,11 @@
         </is>
       </c>
       <c r="Y383" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z383" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52358,9 +52259,7 @@
       <c r="H384" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I384" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I384" s="31" t="n"/>
       <c r="J384" s="31" t="n">
         <v>3600</v>
       </c>
@@ -52413,11 +52312,11 @@
         </is>
       </c>
       <c r="Y384" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z384" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -52454,9 +52353,7 @@
       <c r="H385" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I385" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I385" s="31" t="n"/>
       <c r="J385" s="31" t="n">
         <v>4000</v>
       </c>
@@ -52509,11 +52406,11 @@
         </is>
       </c>
       <c r="Y385" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z385" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52550,9 +52447,7 @@
       <c r="H386" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I386" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I386" s="31" t="n"/>
       <c r="J386" s="31" t="n">
         <v>5000</v>
       </c>
@@ -52605,11 +52500,11 @@
         </is>
       </c>
       <c r="Y386" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z386" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52646,9 +52541,7 @@
       <c r="H387" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I387" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I387" s="31" t="n"/>
       <c r="J387" s="31" t="n">
         <v>4400</v>
       </c>
@@ -52701,11 +52594,11 @@
         </is>
       </c>
       <c r="Y387" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z387" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52742,9 +52635,7 @@
       <c r="H388" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I388" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I388" s="31" t="n"/>
       <c r="J388" s="31" t="n">
         <v>4000</v>
       </c>
@@ -52797,11 +52688,11 @@
         </is>
       </c>
       <c r="Y388" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z388" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -52838,9 +52729,7 @@
       <c r="H389" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I389" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I389" s="31" t="n"/>
       <c r="J389" s="31" t="n">
         <v>4000</v>
       </c>
@@ -52893,9 +52782,13 @@
         </is>
       </c>
       <c r="Y389" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z389" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z389" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="31" t="n">
@@ -52930,9 +52823,7 @@
       <c r="H390" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I390" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I390" s="31" t="n"/>
       <c r="J390" s="31" t="n">
         <v>6000</v>
       </c>
@@ -52985,11 +52876,11 @@
         </is>
       </c>
       <c r="Y390" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z390" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -53026,9 +52917,7 @@
       <c r="H391" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I391" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I391" s="31" t="n"/>
       <c r="J391" s="31" t="n">
         <v>3200</v>
       </c>
@@ -53081,11 +52970,11 @@
         </is>
       </c>
       <c r="Y391" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z391" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -53122,9 +53011,7 @@
       <c r="H392" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I392" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I392" s="31" t="n"/>
       <c r="J392" s="31" t="n">
         <v>3000</v>
       </c>
@@ -53177,11 +53064,11 @@
         </is>
       </c>
       <c r="Y392" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z392" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -53218,9 +53105,7 @@
       <c r="H393" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I393" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I393" s="31" t="n"/>
       <c r="J393" s="31" t="n">
         <v>5000</v>
       </c>
@@ -53273,11 +53158,11 @@
         </is>
       </c>
       <c r="Y393" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z393" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -53314,9 +53199,7 @@
       <c r="H394" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I394" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I394" s="31" t="n"/>
       <c r="J394" s="31" t="n">
         <v>4400</v>
       </c>
@@ -53369,11 +53252,11 @@
         </is>
       </c>
       <c r="Y394" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z394" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -53410,9 +53293,7 @@
       <c r="H395" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="I395" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I395" s="31" t="n"/>
       <c r="J395" s="31" t="n">
         <v>5000</v>
       </c>
@@ -53465,11 +53346,11 @@
         </is>
       </c>
       <c r="Y395" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z395" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -53506,9 +53387,7 @@
       <c r="H396" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I396" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I396" s="31" t="n"/>
       <c r="J396" s="31" t="n">
         <v>1800</v>
       </c>
@@ -53602,9 +53481,7 @@
       <c r="H397" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I397" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I397" s="31" t="n"/>
       <c r="J397" s="31" t="n">
         <v>2400</v>
       </c>
@@ -53698,9 +53575,7 @@
       <c r="H398" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I398" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I398" s="31" t="n"/>
       <c r="J398" s="31" t="n">
         <v>2800</v>
       </c>
@@ -53753,11 +53628,11 @@
         </is>
       </c>
       <c r="Y398" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z398" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -53794,9 +53669,7 @@
       <c r="H399" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I399" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I399" s="31" t="n"/>
       <c r="J399" s="31" t="n">
         <v>3200</v>
       </c>
@@ -53849,11 +53722,11 @@
         </is>
       </c>
       <c r="Y399" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z399" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -53890,9 +53763,7 @@
       <c r="H400" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I400" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I400" s="31" t="n"/>
       <c r="J400" s="31" t="n">
         <v>3000</v>
       </c>
@@ -53945,11 +53816,11 @@
         </is>
       </c>
       <c r="Y400" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z400" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -53986,9 +53857,7 @@
       <c r="H401" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I401" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I401" s="31" t="n"/>
       <c r="J401" s="31" t="n">
         <v>2400</v>
       </c>
@@ -54078,9 +53947,7 @@
       <c r="H402" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I402" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I402" s="31" t="n"/>
       <c r="J402" s="31" t="n">
         <v>2400</v>
       </c>
@@ -54174,9 +54041,7 @@
       <c r="H403" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I403" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I403" s="31" t="n"/>
       <c r="J403" s="31" t="n">
         <v>3200</v>
       </c>
@@ -54229,11 +54094,11 @@
         </is>
       </c>
       <c r="Y403" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z403" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -54270,9 +54135,7 @@
       <c r="H404" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="I404" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I404" s="31" t="n"/>
       <c r="J404" s="31" t="n">
         <v>3600</v>
       </c>
@@ -54325,11 +54188,11 @@
         </is>
       </c>
       <c r="Y404" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z404" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -54366,9 +54229,7 @@
       <c r="H405" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I405" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I405" s="31" t="n"/>
       <c r="J405" s="31" t="n">
         <v>2800</v>
       </c>
@@ -54421,11 +54282,11 @@
         </is>
       </c>
       <c r="Y405" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z405" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -54462,9 +54323,7 @@
       <c r="H406" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I406" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I406" s="31" t="n"/>
       <c r="J406" s="31" t="n">
         <v>3600</v>
       </c>
@@ -54517,11 +54376,11 @@
         </is>
       </c>
       <c r="Y406" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z406" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -54558,9 +54417,7 @@
       <c r="H407" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I407" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I407" s="31" t="n"/>
       <c r="J407" s="31" t="n">
         <v>5000</v>
       </c>
@@ -54613,11 +54470,11 @@
         </is>
       </c>
       <c r="Y407" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z407" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -54654,9 +54511,7 @@
       <c r="H408" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I408" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I408" s="31" t="n"/>
       <c r="J408" s="31" t="n">
         <v>4000</v>
       </c>
@@ -54709,11 +54564,11 @@
         </is>
       </c>
       <c r="Y408" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z408" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -54750,9 +54605,7 @@
       <c r="H409" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I409" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I409" s="31" t="n"/>
       <c r="J409" s="31" t="n">
         <v>2400</v>
       </c>
@@ -54846,9 +54699,7 @@
       <c r="H410" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I410" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I410" s="31" t="n"/>
       <c r="J410" s="31" t="n">
         <v>2400</v>
       </c>
@@ -54942,9 +54793,7 @@
       <c r="H411" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I411" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I411" s="31" t="n"/>
       <c r="J411" s="31" t="n">
         <v>4000</v>
       </c>
@@ -54997,11 +54846,11 @@
         </is>
       </c>
       <c r="Y411" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z411" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -55038,9 +54887,7 @@
       <c r="H412" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I412" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I412" s="31" t="n"/>
       <c r="J412" s="31" t="n">
         <v>2000</v>
       </c>
@@ -55130,9 +54977,7 @@
       <c r="H413" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I413" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I413" s="31" t="n"/>
       <c r="J413" s="31" t="n">
         <v>4000</v>
       </c>
@@ -55185,11 +55030,11 @@
         </is>
       </c>
       <c r="Y413" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z413" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -55226,9 +55071,7 @@
       <c r="H414" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I414" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I414" s="31" t="n"/>
       <c r="J414" s="31" t="n">
         <v>2400</v>
       </c>
@@ -55318,9 +55161,7 @@
       <c r="H415" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="I415" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I415" s="31" t="n"/>
       <c r="J415" s="31" t="n">
         <v>3600</v>
       </c>
@@ -55373,11 +55214,11 @@
         </is>
       </c>
       <c r="Y415" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z415" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -55414,9 +55255,7 @@
       <c r="H416" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I416" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I416" s="31" t="n"/>
       <c r="J416" s="31" t="n">
         <v>3200</v>
       </c>
@@ -55469,11 +55308,11 @@
         </is>
       </c>
       <c r="Y416" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z416" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -55510,9 +55349,7 @@
       <c r="H417" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I417" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I417" s="31" t="n"/>
       <c r="J417" s="31" t="n">
         <v>4000</v>
       </c>
@@ -55565,11 +55402,11 @@
         </is>
       </c>
       <c r="Y417" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z417" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -55606,9 +55443,7 @@
       <c r="H418" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I418" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I418" s="31" t="n"/>
       <c r="J418" s="31" t="n">
         <v>2400</v>
       </c>
@@ -55698,9 +55533,7 @@
       <c r="H419" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I419" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I419" s="31" t="n"/>
       <c r="J419" s="31" t="n">
         <v>1600</v>
       </c>
@@ -55790,9 +55623,7 @@
       <c r="H420" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I420" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I420" s="31" t="n"/>
       <c r="J420" s="31" t="n">
         <v>2800</v>
       </c>
@@ -55845,11 +55676,11 @@
         </is>
       </c>
       <c r="Y420" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z420" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -55886,9 +55717,7 @@
       <c r="H421" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I421" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I421" s="31" t="n"/>
       <c r="J421" s="31" t="n">
         <v>3000</v>
       </c>
@@ -55941,11 +55770,11 @@
         </is>
       </c>
       <c r="Y421" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z421" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -55982,9 +55811,7 @@
       <c r="H422" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I422" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I422" s="31" t="n"/>
       <c r="J422" s="31" t="n">
         <v>5000</v>
       </c>
@@ -56037,11 +55864,11 @@
         </is>
       </c>
       <c r="Y422" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z422" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56078,9 +55905,7 @@
       <c r="H423" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I423" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I423" s="31" t="n"/>
       <c r="J423" s="31" t="n">
         <v>5000</v>
       </c>
@@ -56133,9 +55958,13 @@
         </is>
       </c>
       <c r="Y423" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z423" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z423" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="31" t="n">
@@ -56170,9 +55999,7 @@
       <c r="H424" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I424" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I424" s="31" t="n"/>
       <c r="J424" s="31" t="n">
         <v>7000</v>
       </c>
@@ -56225,11 +56052,11 @@
         </is>
       </c>
       <c r="Y424" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z424" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56266,9 +56093,7 @@
       <c r="H425" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I425" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I425" s="31" t="n"/>
       <c r="J425" s="31" t="n">
         <v>4600</v>
       </c>
@@ -56321,9 +56146,13 @@
         </is>
       </c>
       <c r="Y425" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z425" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z425" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="31" t="n">
@@ -56358,9 +56187,7 @@
       <c r="H426" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I426" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I426" s="31" t="n"/>
       <c r="J426" s="31" t="n">
         <v>6000</v>
       </c>
@@ -56413,11 +56240,11 @@
         </is>
       </c>
       <c r="Y426" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z426" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56454,9 +56281,7 @@
       <c r="H427" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I427" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I427" s="31" t="n"/>
       <c r="J427" s="31" t="n">
         <v>8000</v>
       </c>
@@ -56509,11 +56334,11 @@
         </is>
       </c>
       <c r="Y427" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z427" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56550,9 +56375,7 @@
       <c r="H428" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I428" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I428" s="31" t="n"/>
       <c r="J428" s="31" t="n">
         <v>8000</v>
       </c>
@@ -56605,11 +56428,11 @@
         </is>
       </c>
       <c r="Y428" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z428" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56646,9 +56469,7 @@
       <c r="H429" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I429" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I429" s="31" t="n"/>
       <c r="J429" s="31" t="n">
         <v>8000</v>
       </c>
@@ -56701,11 +56522,11 @@
         </is>
       </c>
       <c r="Y429" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z429" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56742,9 +56563,7 @@
       <c r="H430" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I430" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I430" s="31" t="n"/>
       <c r="J430" s="31" t="n">
         <v>5600</v>
       </c>
@@ -56797,11 +56616,11 @@
         </is>
       </c>
       <c r="Y430" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z430" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -56838,9 +56657,7 @@
       <c r="H431" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I431" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I431" s="31" t="n"/>
       <c r="J431" s="31" t="n">
         <v>10000</v>
       </c>
@@ -56893,11 +56710,11 @@
         </is>
       </c>
       <c r="Y431" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z431" s="31" t="inlineStr">
         <is>
-          <t>牡</t>
+          <t>牡・2500万+</t>
         </is>
       </c>
     </row>
@@ -56934,9 +56751,7 @@
       <c r="H432" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I432" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I432" s="31" t="n"/>
       <c r="J432" s="31" t="n">
         <v>5000</v>
       </c>
@@ -56989,11 +56804,11 @@
         </is>
       </c>
       <c r="Y432" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z432" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -57030,9 +56845,7 @@
       <c r="H433" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I433" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I433" s="31" t="n"/>
       <c r="J433" s="31" t="n">
         <v>5000</v>
       </c>
@@ -57085,11 +56898,11 @@
         </is>
       </c>
       <c r="Y433" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z433" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -57126,9 +56939,7 @@
       <c r="H434" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I434" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I434" s="31" t="n"/>
       <c r="J434" s="31" t="n">
         <v>4000</v>
       </c>
@@ -57181,9 +56992,13 @@
         </is>
       </c>
       <c r="Y434" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z434" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z434" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="31" t="n">
@@ -57218,9 +57033,7 @@
       <c r="H435" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I435" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I435" s="31" t="n"/>
       <c r="J435" s="31" t="n">
         <v>4000</v>
       </c>
@@ -57273,11 +57086,11 @@
         </is>
       </c>
       <c r="Y435" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z435" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -57314,9 +57127,7 @@
       <c r="H436" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I436" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I436" s="31" t="n"/>
       <c r="J436" s="31" t="n">
         <v>4400</v>
       </c>
@@ -57369,11 +57180,11 @@
         </is>
       </c>
       <c r="Y436" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z436" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -57410,9 +57221,7 @@
       <c r="H437" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I437" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I437" s="31" t="n"/>
       <c r="J437" s="31" t="n">
         <v>3000</v>
       </c>
@@ -57465,11 +57274,11 @@
         </is>
       </c>
       <c r="Y437" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z437" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -57506,9 +57315,7 @@
       <c r="H438" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I438" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I438" s="31" t="n"/>
       <c r="J438" s="31" t="n">
         <v>7000</v>
       </c>
@@ -57561,9 +57368,13 @@
         </is>
       </c>
       <c r="Y438" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z438" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z438" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="31" t="n">
@@ -57598,9 +57409,7 @@
       <c r="H439" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I439" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I439" s="31" t="n"/>
       <c r="J439" s="31" t="n">
         <v>3200</v>
       </c>
@@ -57653,11 +57462,11 @@
         </is>
       </c>
       <c r="Y439" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z439" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -57694,9 +57503,7 @@
       <c r="H440" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I440" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I440" s="31" t="n"/>
       <c r="J440" s="31" t="n">
         <v>3000</v>
       </c>
@@ -57749,11 +57556,11 @@
         </is>
       </c>
       <c r="Y440" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z440" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯</t>
+          <t>牡・2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -57790,9 +57597,7 @@
       <c r="H441" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I441" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I441" s="31" t="n"/>
       <c r="J441" s="31" t="n">
         <v>2800</v>
       </c>
@@ -57845,11 +57650,11 @@
         </is>
       </c>
       <c r="Y441" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z441" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -57886,9 +57691,7 @@
       <c r="H442" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I442" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I442" s="31" t="n"/>
       <c r="J442" s="31" t="n">
         <v>5000</v>
       </c>
@@ -57941,11 +57744,11 @@
         </is>
       </c>
       <c r="Y442" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z442" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -57982,9 +57785,7 @@
       <c r="H443" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="I443" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I443" s="31" t="n"/>
       <c r="J443" s="31" t="n">
         <v>3000</v>
       </c>
@@ -58037,11 +57838,11 @@
         </is>
       </c>
       <c r="Y443" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z443" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -58078,9 +57879,7 @@
       <c r="H444" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I444" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I444" s="31" t="n"/>
       <c r="J444" s="31" t="n">
         <v>3000</v>
       </c>
@@ -58133,11 +57932,11 @@
         </is>
       </c>
       <c r="Y444" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z444" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -58174,9 +57973,7 @@
       <c r="H445" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I445" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I445" s="31" t="n"/>
       <c r="J445" s="31" t="n">
         <v>2400</v>
       </c>
@@ -58266,9 +58063,7 @@
       <c r="H446" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="I446" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I446" s="31" t="n"/>
       <c r="J446" s="31" t="n">
         <v>4000</v>
       </c>
@@ -58321,11 +58116,11 @@
         </is>
       </c>
       <c r="Y446" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z446" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -58362,9 +58157,7 @@
       <c r="H447" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="I447" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I447" s="31" t="n"/>
       <c r="J447" s="31" t="n">
         <v>4000</v>
       </c>
@@ -58417,11 +58210,11 @@
         </is>
       </c>
       <c r="Y447" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z447" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -58458,9 +58251,7 @@
       <c r="H448" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="I448" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I448" s="31" t="n"/>
       <c r="J448" s="31" t="n">
         <v>2400</v>
       </c>
@@ -58554,9 +58345,7 @@
       <c r="H449" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I449" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I449" s="31" t="n"/>
       <c r="J449" s="31" t="n">
         <v>5000</v>
       </c>
@@ -58609,9 +58398,13 @@
         </is>
       </c>
       <c r="Y449" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z449" s="31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z449" s="31" t="inlineStr">
+        <is>
+          <t>2500万+</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="31" t="n">
@@ -58646,9 +58439,7 @@
       <c r="H450" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="I450" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I450" s="31" t="n"/>
       <c r="J450" s="31" t="n">
         <v>3600</v>
       </c>
@@ -58701,11 +58492,11 @@
         </is>
       </c>
       <c r="Y450" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z450" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -58742,9 +58533,7 @@
       <c r="H451" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I451" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I451" s="31" t="n"/>
       <c r="J451" s="31" t="n">
         <v>3000</v>
       </c>
@@ -58797,11 +58586,11 @@
         </is>
       </c>
       <c r="Y451" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z451" s="31" t="inlineStr">
         <is>
-          <t>価格帯・420kg+</t>
+          <t>2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -58838,9 +58627,7 @@
       <c r="H452" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I452" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I452" s="31" t="n"/>
       <c r="J452" s="31" t="n">
         <v>4000</v>
       </c>
@@ -58893,11 +58680,11 @@
         </is>
       </c>
       <c r="Y452" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z452" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -58934,9 +58721,7 @@
       <c r="H453" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I453" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I453" s="31" t="n"/>
       <c r="J453" s="31" t="n">
         <v>4000</v>
       </c>
@@ -58989,11 +58774,11 @@
         </is>
       </c>
       <c r="Y453" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z453" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -59030,9 +58815,7 @@
       <c r="H454" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="I454" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I454" s="31" t="n"/>
       <c r="J454" s="31" t="n">
         <v>4400</v>
       </c>
@@ -59085,11 +58868,11 @@
         </is>
       </c>
       <c r="Y454" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z454" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -59126,9 +58909,7 @@
       <c r="H455" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I455" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I455" s="31" t="n"/>
       <c r="J455" s="31" t="n">
         <v>2000</v>
       </c>
@@ -59222,9 +59003,7 @@
       <c r="H456" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I456" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I456" s="31" t="n"/>
       <c r="J456" s="31" t="n">
         <v>3200</v>
       </c>
@@ -59277,11 +59056,11 @@
         </is>
       </c>
       <c r="Y456" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z456" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -59318,9 +59097,7 @@
       <c r="H457" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I457" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I457" s="31" t="n"/>
       <c r="J457" s="31" t="n">
         <v>5000</v>
       </c>
@@ -59373,11 +59150,11 @@
         </is>
       </c>
       <c r="Y457" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z457" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -59414,9 +59191,7 @@
       <c r="H458" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I458" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I458" s="31" t="n"/>
       <c r="J458" s="31" t="n">
         <v>3000</v>
       </c>
@@ -59469,11 +59244,11 @@
         </is>
       </c>
       <c r="Y458" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z458" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -59510,9 +59285,7 @@
       <c r="H459" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="I459" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I459" s="31" t="n"/>
       <c r="J459" s="31" t="n">
         <v>3000</v>
       </c>
@@ -59565,11 +59338,11 @@
         </is>
       </c>
       <c r="Y459" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z459" s="31" t="inlineStr">
         <is>
-          <t>価格帯</t>
+          <t>2500万+・4000万未満</t>
         </is>
       </c>
     </row>
@@ -59606,9 +59379,7 @@
       <c r="H460" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I460" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I460" s="31" t="n"/>
       <c r="J460" s="31" t="n">
         <v>2400</v>
       </c>
@@ -59702,9 +59473,7 @@
       <c r="H461" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="I461" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I461" s="31" t="n"/>
       <c r="J461" s="31" t="n">
         <v>4000</v>
       </c>
@@ -59757,11 +59526,11 @@
         </is>
       </c>
       <c r="Y461" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z461" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -59798,9 +59567,7 @@
       <c r="H462" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="I462" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I462" s="31" t="n"/>
       <c r="J462" s="31" t="n">
         <v>6000</v>
       </c>
@@ -59853,11 +59620,11 @@
         </is>
       </c>
       <c r="Y462" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z462" s="31" t="inlineStr">
         <is>
-          <t>牡・420kg+</t>
+          <t>牡・2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -59894,9 +59661,7 @@
       <c r="H463" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I463" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I463" s="31" t="n"/>
       <c r="J463" s="31" t="n">
         <v>4000</v>
       </c>
@@ -59949,11 +59714,11 @@
         </is>
       </c>
       <c r="Y463" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z463" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -59990,9 +59755,7 @@
       <c r="H464" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="I464" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I464" s="31" t="n"/>
       <c r="J464" s="31" t="n">
         <v>5000</v>
       </c>
@@ -60045,11 +59808,11 @@
         </is>
       </c>
       <c r="Y464" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z464" s="31" t="inlineStr">
         <is>
-          <t>420kg+</t>
+          <t>2500万+・420kg+</t>
         </is>
       </c>
     </row>
@@ -60086,9 +59849,7 @@
       <c r="H465" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I465" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I465" s="31" t="n"/>
       <c r="J465" s="31" t="n">
         <v>2500</v>
       </c>
@@ -60141,11 +59902,11 @@
         </is>
       </c>
       <c r="Y465" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z465" s="31" t="inlineStr">
         <is>
-          <t>牡・価格帯・420kg+</t>
+          <t>牡・2500万+・4000万未満・420kg+</t>
         </is>
       </c>
     </row>
@@ -60182,9 +59943,7 @@
       <c r="H466" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="I466" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I466" s="31" t="n"/>
       <c r="J466" s="31" t="n">
         <v>2000</v>
       </c>
@@ -60278,9 +60037,7 @@
       <c r="H467" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="I467" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I467" s="31" t="n"/>
       <c r="J467" s="31" t="n">
         <v>2000</v>
       </c>
@@ -60374,9 +60131,7 @@
       <c r="H468" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="I468" s="31" t="n">
-        <v>1</v>
-      </c>
+      <c r="I468" s="31" t="n"/>
       <c r="J468" s="31" t="n">
         <v>1800</v>
       </c>
